--- a/Results/noise_corrected/2_amp_function_by_season/calculations/storm2_results.xlsx
+++ b/Results/noise_corrected/2_amp_function_by_season/calculations/storm2_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\huck4481\Documents\GitHub\shear_stress_paper\Results\noise_corrected\2_amp_function_by_season\calculations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{731C3673-46D4-4FD9-A530-558E50627B1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F71BB1B-E670-4CDA-AB19-6D6F1C9B3921}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{867F3169-A9A3-4AE6-89E2-304587BC45FE}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="47">
   <si>
     <t>max_amp</t>
   </si>
@@ -320,7 +320,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -506,6 +506,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -667,7 +673,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -684,6 +690,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="22" fontId="0" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -823,6 +831,623 @@
         <c:scatterStyle val="smoothMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>storm2_results!$I$33</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>tau</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>storm2_results!$E$34:$E$125</c:f>
+              <c:numCache>
+                <c:formatCode>m/d/yyyy\ h:mm</c:formatCode>
+                <c:ptCount val="92"/>
+                <c:pt idx="0">
+                  <c:v>44776.000694444447</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>44776.011111111111</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>44776.021527777775</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>44776.031944444447</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>44776.042361111111</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>44776.052777777775</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>44776.063194444447</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>44776.073611111111</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>44776.084027777775</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>44776.094444444447</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>44776.104861111111</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>44776.115277777775</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>44776.125694444447</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>44776.136111111111</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>44776.146527777775</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>44776.156944444447</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>44776.167361111111</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>44776.177777777775</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>44776.188194444447</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>44776.198611111111</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>44776.209027777775</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>44776.219444444447</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>44776.229861111111</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>44776.240277777775</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>44776.250694444447</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>44776.261111111111</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>44776.271527777775</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>44776.281944444447</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>44776.292361111111</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>44776.302777777775</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>44776.313194444447</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>44776.323611111111</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>44776.334027777775</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>44776.344444444447</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>44776.354861111111</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>44776.365277777775</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>44776.375694444447</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>44776.386111111111</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>44776.396527777775</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>44776.406944444447</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>44776.417361111111</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>44776.427777777775</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>44776.438194444447</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>44776.448611111111</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>44776.459027777775</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>44776.469444444447</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>44776.479861111111</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>44776.490277777775</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>44776.500694444447</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>44776.511111111111</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>44776.521527777775</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>44776.531944444447</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>44776.542361111111</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>44776.552777777775</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>44776.563194444447</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>44776.573611111111</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>44776.584027777775</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>44776.594444444447</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>44776.604861111111</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>44776.615277777775</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>44776.625694444447</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>44776.636111111111</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>44776.646527777775</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>44776.656944444447</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>44776.667361111111</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>44776.677777777775</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>44776.688194444447</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>44776.698611111111</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>44776.709027777775</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>44776.719444444447</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>44776.729861111111</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>44776.740277777775</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>44776.750694444447</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>44776.761111111111</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>44776.771527777775</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>44776.781944444447</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>44776.792361111111</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>44776.802777777775</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>44776.813194444447</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>44776.823611111111</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>44776.834027777775</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>44776.844444444447</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>44776.854861111111</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>44776.865277777775</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>44776.875694444447</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>44776.917361111111</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>44776.948611111111</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>44776.959027777775</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>44776.969444444447</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>44776.979861111111</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>44776.990277777775</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>44777.000694444447</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>storm2_results!$I$34:$I$125</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="92"/>
+                <c:pt idx="0">
+                  <c:v>0.76957219099999996</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.771817164</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.78552173950000004</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.77333739349999997</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.69855224699999996</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.71226070049999901</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.773592222</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.76798645399999999</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.7563906655</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.72541048299999999</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.74867457049999997</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.77382161049999998</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.75131557849999997</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.75904434850000002</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.67891565050000002</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.70024108200000001</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.740701163</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.74046465699999997</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.74873955049999996</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.73845619600000001</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.726575334499999</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.78202204350000004</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.83594533650000002</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.78025976949999998</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.75657462549999999</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.70298291499999999</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.68254177999999999</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.684465781</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.69437548549999994</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.7037178785</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.672222341</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.67980481400000004</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.74230587949999904</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.76352864149999999</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.72191215399999997</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.72191215399999997</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.77710206100000001</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.73831050949999999</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.65388842250000001</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.66321230600000003</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.73972780449999997</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.72333429699999996</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.71002781749999999</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.72868923050000001</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.66863318549999995</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.65794700399999995</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.69552619199999999</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.73331566249999902</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.74682702999999995</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.76967573</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.7477791265</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.71824162000000003</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.72944691949999996</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.68032893350000001</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.62184915699999999</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.63156217000000003</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.66496995749999999</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.67182250649999997</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.69815132099999999</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1.3141996124999999</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>12.6789259225</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>22.620213794999898</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>19.508647905</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>15.20489341</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>17.173613769999999</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>19.879890565</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>18.271869219999999</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>17.106053899999999</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>15.6821315249999</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>15.17592808</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>14.28611474</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>11.657254006500001</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>9.6026396404999996</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>9.2022879035000003</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>7.7941709709999998</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>5.7733400259999996</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>5.1560535449999998</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>4.4556949205</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>3.5644504299999999</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>3.44414985149999</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>3.4561308749999999</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>3.188326338</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>2.8661624744999998</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>2.6512377974999999</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>2.6445850609999999</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>2.3885584199999998</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>2.4828400044999999</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>2.5050373965000001</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>2.248553292</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>2.1564305309999998</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>2.2236830264999998</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>2.2059633774999998</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4AD4-4D8E-A261-D0ECE1E5C5A3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="541374511"/>
+        <c:axId val="382721663"/>
+      </c:scatterChart>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:spPr>
@@ -1141,280 +1766,280 @@
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="92"/>
                 <c:pt idx="0">
-                  <c:v>9.4170832457325001E-10</c:v>
+                  <c:v>1.4221254009907999E-7</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.19225420553501E-9</c:v>
+                  <c:v>1.79726955104284E-7</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.13718472474984E-9</c:v>
+                  <c:v>1.69582018075944E-7</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.0151142238303101E-9</c:v>
+                  <c:v>1.52839039433596E-7</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6.4398678510234201E-10</c:v>
+                  <c:v>1.0321196451396E-7</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6.2715093817983104E-10</c:v>
+                  <c:v>9.9320847969424001E-8</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>9.9990196305767197E-10</c:v>
+                  <c:v>1.5051816349752101E-7</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.02326911631512E-9</c:v>
+                  <c:v>1.54725410758714E-7</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>9.5971722737034707E-10</c:v>
+                  <c:v>1.4647853697863599E-7</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>7.9877157460493596E-10</c:v>
+                  <c:v>1.250864956627E-7</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>9.7700202241142105E-10</c:v>
+                  <c:v>1.5005887693287601E-7</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>9.4746727011196394E-10</c:v>
+                  <c:v>1.4259904240921899E-7</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>9.9179274251827295E-10</c:v>
+                  <c:v>1.52001438766829E-7</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>9.0412029372403197E-10</c:v>
+                  <c:v>1.3769639682143201E-7</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>6.1770763270172503E-10</c:v>
+                  <c:v>1.00749518391823E-7</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>6.6201536184373002E-10</c:v>
+                  <c:v>1.05944141049072E-7</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>8.0323787221929904E-10</c:v>
+                  <c:v>1.24184369088094E-7</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>8.9163950421949099E-10</c:v>
+                  <c:v>1.37878724988046E-7</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>7.8059713555551002E-10</c:v>
+                  <c:v>1.19886430033326E-7</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>8.1405890757249299E-10</c:v>
+                  <c:v>1.2609225603872499E-7</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>7.7083428546008703E-10</c:v>
+                  <c:v>1.20592636157517E-7</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>9.9394579461837903E-10</c:v>
+                  <c:v>1.4862872126020399E-7</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1.2167593713498799E-9</c:v>
+                  <c:v>1.7464465475407299E-7</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>9.9761659609293507E-10</c:v>
+                  <c:v>1.49384516203063E-7</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>8.6240978978739599E-10</c:v>
+                  <c:v>1.31607155934079E-7</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>6.2067528552950298E-10</c:v>
+                  <c:v>9.9090210221863701E-8</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>5.4594806038022402E-10</c:v>
+                  <c:v>8.8754463725521903E-8</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>5.2090447587157199E-10</c:v>
+                  <c:v>8.4536834987216905E-8</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>5.8306301614118296E-10</c:v>
+                  <c:v>9.37925917280448E-8</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>6.8948522561471099E-10</c:v>
+                  <c:v>1.10005014672529E-7</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>4.5233308144590302E-10</c:v>
+                  <c:v>7.42269507867231E-8</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>5.1388836432907001E-10</c:v>
+                  <c:v>8.37489976291492E-8</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>8.7150875242922001E-10</c:v>
+                  <c:v>1.3456036196529701E-7</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>8.5961704616773898E-10</c:v>
+                  <c:v>1.3044573565671401E-7</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>6.8942732597906497E-10</c:v>
+                  <c:v>1.0828443230519701E-7</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>6.2702083736231303E-10</c:v>
+                  <c:v>9.84825997732359E-8</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>8.5293857979288797E-10</c:v>
+                  <c:v>1.2803878825587399E-7</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>8.1528735054230495E-10</c:v>
+                  <c:v>1.2629784050930401E-7</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>5.0022108606043999E-10</c:v>
+                  <c:v>8.3491559530010094E-8</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>4.6844564912095302E-10</c:v>
+                  <c:v>7.7510850378197098E-8</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>9.4067720518393391E-10</c:v>
+                  <c:v>1.45550665327585E-7</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>6.5682430527547602E-10</c:v>
+                  <c:v>1.03039015709554E-7</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>6.3892786223280001E-10</c:v>
+                  <c:v>1.0138129644085801E-7</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>7.1708642457303E-10</c:v>
+                  <c:v>1.11984058743973E-7</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>4.5867702983181802E-10</c:v>
+                  <c:v>7.5515919884758005E-8</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>5.3868177925949697E-10</c:v>
+                  <c:v>8.9569897468822199E-8</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>6.1779634236488301E-10</c:v>
+                  <c:v>9.9278824374308606E-8</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>7.3499520574830097E-10</c:v>
+                  <c:v>1.1433540602737001E-7</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>9.4909688375402305E-10</c:v>
+                  <c:v>1.45994317995278E-7</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>8.8232007600894004E-10</c:v>
+                  <c:v>1.3323298366791201E-7</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>8.3121502177750504E-10</c:v>
+                  <c:v>1.27761173164764E-7</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>7.5270898989416299E-10</c:v>
+                  <c:v>1.18594503912163E-7</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>8.2191583823346199E-10</c:v>
+                  <c:v>1.2827286419484501E-7</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>5.0678380596177797E-10</c:v>
+                  <c:v>8.2552067113168302E-8</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>3.2699546023203698E-10</c:v>
+                  <c:v>5.6289250569251201E-8</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>4.72004980013671E-10</c:v>
+                  <c:v>8.0481383774328897E-8</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>5.4989495226542702E-10</c:v>
+                  <c:v>9.0839956727602702E-8</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>6.6930170633289299E-10</c:v>
+                  <c:v>1.0987121629035801E-7</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>1.0489946937872801E-9</c:v>
+                  <c:v>1.6818201192618799E-7</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>2.3911052353288801E-8</c:v>
+                  <c:v>2.59925867337766E-6</c:v>
                 </c:pt>
                 <c:pt idx="60" formatCode="General">
-                  <c:v>8.4256581576265999E-4</c:v>
+                  <c:v>2.2757340169528399E-2</c:v>
                 </c:pt>
                 <c:pt idx="61" formatCode="General">
-                  <c:v>3.0194890839779602E-3</c:v>
+                  <c:v>6.88792344191058E-3</c:v>
                 </c:pt>
                 <c:pt idx="62" formatCode="General">
-                  <c:v>1.3419280710164001E-3</c:v>
+                  <c:v>5.7579781162764004E-3</c:v>
                 </c:pt>
                 <c:pt idx="63" formatCode="General">
-                  <c:v>4.3902523980032999E-4</c:v>
+                  <c:v>5.4595327590182402E-3</c:v>
                 </c:pt>
                 <c:pt idx="64" formatCode="General">
-                  <c:v>6.5939852060204699E-4</c:v>
+                  <c:v>4.8759650107001798E-3</c:v>
                 </c:pt>
                 <c:pt idx="65" formatCode="General">
-                  <c:v>1.3813185597794501E-3</c:v>
+                  <c:v>5.4686815441540304E-3</c:v>
                 </c:pt>
                 <c:pt idx="66" formatCode="General">
-                  <c:v>9.8204166941528396E-4</c:v>
+                  <c:v>5.5732365802783701E-3</c:v>
                 </c:pt>
                 <c:pt idx="67" formatCode="General">
-                  <c:v>6.8230783756815302E-4</c:v>
+                  <c:v>5.13099269333694E-3</c:v>
                 </c:pt>
                 <c:pt idx="68" formatCode="General">
-                  <c:v>4.8825608108944398E-4</c:v>
+                  <c:v>5.3212337093761601E-3</c:v>
                 </c:pt>
                 <c:pt idx="69" formatCode="General">
-                  <c:v>4.0077653523385402E-4</c:v>
+                  <c:v>5.0246263053807796E-3</c:v>
                 </c:pt>
                 <c:pt idx="70" formatCode="General">
-                  <c:v>2.8406229446980902E-4</c:v>
+                  <c:v>4.6094203043980297E-3</c:v>
                 </c:pt>
                 <c:pt idx="71" formatCode="General">
-                  <c:v>1.15579019054127E-4</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>4.8066690553333703E-5</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>3.9194224418457197E-5</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>2.2204912325750299E-5</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>5.7209591914661297E-6</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>4.6235635463227896E-6</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>2.0442095213971602E-6</c:v>
+                  <c:v>3.2871035946504899E-3</c:v>
+                </c:pt>
+                <c:pt idx="72" formatCode="General">
+                  <c:v>1.53994824810323E-3</c:v>
+                </c:pt>
+                <c:pt idx="73" formatCode="General">
+                  <c:v>1.2889775231266999E-3</c:v>
+                </c:pt>
+                <c:pt idx="74" formatCode="General">
+                  <c:v>8.0868477222856099E-4</c:v>
+                </c:pt>
+                <c:pt idx="75" formatCode="General">
+                  <c:v>2.5053512897688302E-4</c:v>
+                </c:pt>
+                <c:pt idx="76" formatCode="General">
+                  <c:v>2.17042463423721E-4</c:v>
+                </c:pt>
+                <c:pt idx="77" formatCode="General">
+                  <c:v>1.0496417991406E-4</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>8.4608754407049798E-7</c:v>
+                  <c:v>4.98276871901227E-5</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>7.9548858694861903E-7</c:v>
+                  <c:v>4.7846362469734101E-5</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>9.2995385842568605E-7</c:v>
+                  <c:v>5.58148706582288E-5</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>7.1353611262290904E-7</c:v>
+                  <c:v>4.5000964263210298E-5</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>4.4749196250294002E-7</c:v>
+                  <c:v>3.0130741794009601E-5</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>2.97598488557786E-7</c:v>
+                  <c:v>2.1020868956811798E-5</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>2.91656407736742E-7</c:v>
+                  <c:v>2.0632970383662501E-5</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>2.38278498467708E-7</c:v>
+                  <c:v>1.7944875951429599E-5</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>2.7142588960351998E-7</c:v>
+                  <c:v>1.99608362478804E-5</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>2.8845317308508E-7</c:v>
+                  <c:v>2.1097365103920101E-5</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>1.7803150855957199E-7</c:v>
+                  <c:v>1.39144874919424E-5</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>1.3568315097894001E-7</c:v>
+                  <c:v>1.08806963286294E-5</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>1.86896842999386E-7</c:v>
+                  <c:v>1.4707523941653399E-5</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>1.5120622219659301E-7</c:v>
+                  <c:v>1.19575360197737E-5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1434,8 +2059,8 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="541374511"/>
-        <c:axId val="382721663"/>
+        <c:axId val="1443499904"/>
+        <c:axId val="1443501824"/>
       </c:scatterChart>
       <c:valAx>
         <c:axId val="541374511"/>
@@ -1520,7 +2145,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="0.00E+00" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1559,6 +2184,69 @@
         </c:txPr>
         <c:crossAx val="541374511"/>
         <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1443501824"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="r"/>
+        <c:numFmt formatCode="0.00E+00" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1443499904"/>
+        <c:crosses val="max"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1443499904"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="t"/>
+        <c:numFmt formatCode="m/d/yyyy\ h:mm" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1443501824"/>
+        <c:crosses val="max"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:spPr>
@@ -2012,280 +2700,280 @@
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="92"/>
                 <c:pt idx="0">
-                  <c:v>6.7817983640293597E-10</c:v>
+                  <c:v>1.0241565744345101E-7</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7.9935488811814302E-10</c:v>
+                  <c:v>1.20499151459588E-7</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>8.0473361940703399E-10</c:v>
+                  <c:v>1.20005438184596E-7</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7.2252814219493303E-10</c:v>
+                  <c:v>1.08786286926953E-7</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.4567946577085499E-10</c:v>
+                  <c:v>7.1429188097304793E-8</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.6111146412390699E-10</c:v>
+                  <c:v>7.30254534228644E-8</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>6.9556006144983501E-10</c:v>
+                  <c:v>1.04704687978662E-7</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>6.7940669377925398E-10</c:v>
+                  <c:v>1.02731019720165E-7</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>6.4767005517130501E-10</c:v>
+                  <c:v>9.8851786152673197E-8</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>5.4184663617276897E-10</c:v>
+                  <c:v>8.4852414708764497E-8</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>6.2835086765185102E-10</c:v>
+                  <c:v>9.6509140572479604E-8</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>7.4436162291078E-10</c:v>
+                  <c:v>1.1203052388438301E-7</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>6.45184550477534E-10</c:v>
+                  <c:v>9.8880517814838898E-8</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>6.5859411579469405E-10</c:v>
+                  <c:v>1.00303065136692E-7</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>4.0783672234896999E-10</c:v>
+                  <c:v>6.65190960647415E-8</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>4.66962373632692E-10</c:v>
+                  <c:v>7.4729274315264904E-8</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>5.92647323868018E-10</c:v>
+                  <c:v>9.1626075600631999E-8</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>5.8876469747462296E-10</c:v>
+                  <c:v>9.1043662179332501E-8</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>5.88856603044077E-10</c:v>
+                  <c:v>9.0438348701767694E-8</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>5.1738292916028E-10</c:v>
+                  <c:v>8.0139140013971602E-8</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>5.1529120463564605E-10</c:v>
+                  <c:v>8.0614375783670403E-8</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>6.6814915093842095E-10</c:v>
+                  <c:v>9.9911035846152306E-8</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>8.8406100913321904E-10</c:v>
+                  <c:v>1.2689158872093E-7</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>6.6604720288510995E-10</c:v>
+                  <c:v>9.9734847598926806E-8</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>5.8611970716859301E-10</c:v>
+                  <c:v>8.9444193016331499E-8</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>4.3424020476832302E-10</c:v>
+                  <c:v>6.9326029535019303E-8</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>3.8182657244080302E-10</c:v>
+                  <c:v>6.2073327359061195E-8</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>3.7292213053298599E-10</c:v>
+                  <c:v>6.0520993909596605E-8</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>4.0947433337382098E-10</c:v>
+                  <c:v>6.5868796186162205E-8</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>4.2537444364903198E-10</c:v>
+                  <c:v>6.7867040767186004E-8</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>3.3617646604093302E-10</c:v>
+                  <c:v>5.5165883337354401E-8</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>3.6202863176049598E-10</c:v>
+                  <c:v>5.9000236484766003E-8</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>5.5160123399840004E-10</c:v>
+                  <c:v>8.5166857477847597E-8</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>6.0404134311816401E-10</c:v>
+                  <c:v>9.1662464954226799E-8</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>4.5900594760520299E-10</c:v>
+                  <c:v>7.20934558107596E-8</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>4.6460794079042198E-10</c:v>
+                  <c:v>7.2973329046067995E-8</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>6.6496900461993103E-10</c:v>
+                  <c:v>9.9821754575454596E-8</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>5.6304335255230795E-10</c:v>
+                  <c:v>8.7222203919932196E-8</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>3.3192733722912098E-10</c:v>
+                  <c:v>5.5401764956497602E-8</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>3.3981300122528198E-10</c:v>
+                  <c:v>5.6226789050408003E-8</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>5.9749891916897197E-10</c:v>
+                  <c:v>9.2450805376652304E-8</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>4.9117454685511605E-10</c:v>
+                  <c:v>7.7052784807964101E-8</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>4.3201938664700999E-10</c:v>
+                  <c:v>6.8550282581515004E-8</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>4.9142552613458E-10</c:v>
+                  <c:v>7.6743643584538195E-8</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>3.36586100920068E-10</c:v>
+                  <c:v>5.5415046706262998E-8</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>3.2487796769969299E-10</c:v>
+                  <c:v>5.4019436663800003E-8</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>4.3302363931941802E-10</c:v>
+                  <c:v>6.9586164386871801E-8</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>4.9935639501594296E-10</c:v>
+                  <c:v>7.7679576315849496E-8</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>5.4693488119704999E-10</c:v>
+                  <c:v>8.4131964117135899E-8</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>6.2229837965693897E-10</c:v>
+                  <c:v>9.3968925913969705E-8</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>5.72337455465218E-10</c:v>
+                  <c:v>8.7970624737456199E-8</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>4.6951422905553096E-10</c:v>
+                  <c:v>7.3975211962877299E-8</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>4.7835593819346598E-10</c:v>
+                  <c:v>7.4654950597264206E-8</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>3.7062344732674202E-10</c:v>
+                  <c:v>6.0372354715777496E-8</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>2.4640797211936901E-10</c:v>
+                  <c:v>4.2416858249319797E-8</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>2.5879797023507401E-10</c:v>
+                  <c:v>4.4127540268418999E-8</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>3.2574195123283501E-10</c:v>
+                  <c:v>5.3810977227716901E-8</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>3.87628032659233E-10</c:v>
+                  <c:v>6.3632234929052404E-8</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>4.89366799657478E-10</c:v>
+                  <c:v>7.8458636089864999E-8</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>1.38580466497013E-8</c:v>
+                  <c:v>1.5064434394438E-6</c:v>
                 </c:pt>
                 <c:pt idx="60" formatCode="General">
-                  <c:v>5.5810267175125205E-4</c:v>
+                  <c:v>1.5074113040056999E-2</c:v>
                 </c:pt>
                 <c:pt idx="61" formatCode="General">
-                  <c:v>2.30725901968859E-3</c:v>
+                  <c:v>5.2632160762136997E-3</c:v>
                 </c:pt>
                 <c:pt idx="62" formatCode="General">
-                  <c:v>1.00295106012561E-3</c:v>
+                  <c:v>4.3034871843328102E-3</c:v>
                 </c:pt>
                 <c:pt idx="63" formatCode="General">
-                  <c:v>3.0019692886353901E-4</c:v>
+                  <c:v>3.73312242376734E-3</c:v>
                 </c:pt>
                 <c:pt idx="64" formatCode="General">
-                  <c:v>5.1861207800330098E-4</c:v>
+                  <c:v>3.8349105547707601E-3</c:v>
                 </c:pt>
                 <c:pt idx="65" formatCode="General">
-                  <c:v>1.0531266020267699E-3</c:v>
+                  <c:v>4.1693597551748099E-3</c:v>
                 </c:pt>
                 <c:pt idx="66" formatCode="General">
-                  <c:v>7.1698376637975103E-4</c:v>
+                  <c:v>4.0689924661150003E-3</c:v>
                 </c:pt>
                 <c:pt idx="67" formatCode="General">
-                  <c:v>5.1341501153308496E-4</c:v>
+                  <c:v>3.8609092961429401E-3</c:v>
                 </c:pt>
                 <c:pt idx="68" formatCode="General">
-                  <c:v>3.6351370550483997E-4</c:v>
+                  <c:v>3.9617353648852298E-3</c:v>
                 </c:pt>
                 <c:pt idx="69" formatCode="General">
-                  <c:v>3.0147754661757399E-4</c:v>
+                  <c:v>3.7796923673478599E-3</c:v>
                 </c:pt>
                 <c:pt idx="70" formatCode="General">
-                  <c:v>2.1045785151038799E-4</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>8.5382289286336493E-5</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>3.5339869466431098E-5</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>2.7627215109462799E-5</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>1.37545459257828E-5</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>3.9840848125274297E-6</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>2.6842380066374601E-6</c:v>
+                  <c:v>3.4150561791017799E-3</c:v>
+                </c:pt>
+                <c:pt idx="71" formatCode="General">
+                  <c:v>2.4282991180632702E-3</c:v>
+                </c:pt>
+                <c:pt idx="72" formatCode="General">
+                  <c:v>1.13220963305243E-3</c:v>
+                </c:pt>
+                <c:pt idx="73" formatCode="General">
+                  <c:v>9.0857415429634804E-4</c:v>
+                </c:pt>
+                <c:pt idx="74" formatCode="General">
+                  <c:v>5.0092932934170495E-4</c:v>
+                </c:pt>
+                <c:pt idx="75" formatCode="General">
+                  <c:v>1.7447305057741801E-4</c:v>
+                </c:pt>
+                <c:pt idx="76" formatCode="General">
+                  <c:v>1.2600532544730899E-4</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>1.4058412218177401E-6</c:v>
+                  <c:v>7.2185834863316203E-5</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>5.6447780454141204E-7</c:v>
+                  <c:v>3.3243159845828698E-5</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>5.4522666378771696E-7</c:v>
+                  <c:v>3.2793823835698597E-5</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>6.09978026661199E-7</c:v>
+                  <c:v>3.6610251523688897E-5</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>4.60290903372103E-7</c:v>
+                  <c:v>2.9029412986223601E-5</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>3.0123017056390899E-7</c:v>
+                  <c:v>2.0282573208857299E-5</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>2.3196495809394001E-7</c:v>
+                  <c:v>1.6384844595069299E-5</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>2.23014422514708E-7</c:v>
+                  <c:v>1.57769548440178E-5</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>1.72637766353315E-7</c:v>
+                  <c:v>1.30014387435252E-5</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>1.9534509780769699E-7</c:v>
+                  <c:v>1.43658053952108E-5</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>2.1541480276719E-7</c:v>
+                  <c:v>1.5755364013596901E-5</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>1.33715456593602E-7</c:v>
+                  <c:v>1.04508581839459E-5</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>1.0094948792846299E-7</c:v>
+                  <c:v>8.0953361912696808E-6</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>1.2465689326174701E-7</c:v>
+                  <c:v>9.8096587014311299E-6</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>1.1480211508073799E-7</c:v>
+                  <c:v>9.0786636044787495E-6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2883,280 +3571,280 @@
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="92"/>
                 <c:pt idx="0">
-                  <c:v>6.6705963235866703E-10</c:v>
+                  <c:v>1.0073633442779E-7</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7.8287815236245401E-10</c:v>
+                  <c:v>1.18015357706683E-7</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>7.8143387235638396E-10</c:v>
+                  <c:v>1.16530876805227E-7</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7.0875576954331898E-10</c:v>
+                  <c:v>1.0671267180346699E-7</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.2747369092617503E-10</c:v>
+                  <c:v>6.8511342838640803E-8</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.45093909203132E-10</c:v>
+                  <c:v>7.0488779968203097E-8</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>6.6392990013645499E-10</c:v>
+                  <c:v>9.9943307395675201E-8</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>6.5978128215744202E-10</c:v>
+                  <c:v>9.9763520923234002E-8</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>6.2250654971797597E-10</c:v>
+                  <c:v>9.5011161685906004E-8</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>5.3286742621083799E-10</c:v>
+                  <c:v>8.3446283164622004E-8</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>6.0535869958787201E-10</c:v>
+                  <c:v>9.29777467387017E-8</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>7.3707415853799905E-10</c:v>
+                  <c:v>1.10933720359415E-7</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>6.3212548690507896E-10</c:v>
+                  <c:v>9.6879095171269695E-8</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>6.3424407303283705E-10</c:v>
+                  <c:v>9.6594583892903297E-8</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>4.0384717270957802E-10</c:v>
+                  <c:v>6.5868391454465701E-8</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>4.5209966933268698E-10</c:v>
+                  <c:v>7.2350754825156606E-8</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>5.8212743970692898E-10</c:v>
+                  <c:v>8.9999651819504605E-8</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>5.7397606382619397E-10</c:v>
+                  <c:v>8.8756820982546494E-8</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>5.8515172826811804E-10</c:v>
+                  <c:v>8.9869343015544797E-8</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>5.11387904601465E-10</c:v>
+                  <c:v>7.9210550984000096E-8</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>4.9604013721892498E-10</c:v>
+                  <c:v>7.7602655868289506E-8</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>6.6922468618957803E-10</c:v>
+                  <c:v>1.00071864968304E-7</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>8.5683742196982795E-10</c:v>
+                  <c:v>1.2298411605744001E-7</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>6.48865689616417E-10</c:v>
+                  <c:v>9.7162063567462706E-8</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>5.8022196753551605E-10</c:v>
+                  <c:v>8.8544174547710997E-8</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>4.2592079278639002E-10</c:v>
+                  <c:v>6.7997843442912401E-8</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>3.7585111632660001E-10</c:v>
+                  <c:v>6.1101900878412694E-8</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>3.6676338273875602E-10</c:v>
+                  <c:v>5.95214996260397E-8</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>3.9646036096304999E-10</c:v>
+                  <c:v>6.3775344592046203E-8</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>4.1509363568013599E-10</c:v>
+                  <c:v>6.6226772943665902E-8</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>3.32905053105935E-10</c:v>
+                  <c:v>5.4629051040995798E-8</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>3.5559226663422601E-10</c:v>
+                  <c:v>5.7951294409898098E-8</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>5.4487477046016601E-10</c:v>
+                  <c:v>8.41282960556246E-8</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>5.8966330620128902E-10</c:v>
+                  <c:v>8.9480617106329296E-8</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>4.40987573149627E-10</c:v>
+                  <c:v>6.9263412127430206E-8</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>4.5915625771288198E-10</c:v>
+                  <c:v>7.2117064164911005E-8</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>6.3493447019437199E-10</c:v>
+                  <c:v>9.5313123490926E-8</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>5.5045012158756103E-10</c:v>
+                  <c:v>8.5271360606545198E-8</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>3.1403445702283099E-10</c:v>
+                  <c:v>5.2415276552998997E-8</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>3.3049676507131203E-10</c:v>
+                  <c:v>5.4685288157373297E-8</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>5.7387604940369601E-10</c:v>
+                  <c:v>8.8795646739425097E-8</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>4.8591189854669703E-10</c:v>
+                  <c:v>7.6227209236170099E-8</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>4.2364331779199299E-10</c:v>
+                  <c:v>6.7221217486965405E-8</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>4.7921129578899002E-10</c:v>
+                  <c:v>7.4836203919844605E-8</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>3.2110161961366301E-10</c:v>
+                  <c:v>5.2865704198383603E-8</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>3.1234882234302598E-10</c:v>
+                  <c:v>5.1936139422548101E-8</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>4.2005611076522498E-10</c:v>
+                  <c:v>6.7502304541728903E-8</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>4.8157476699739597E-10</c:v>
+                  <c:v>7.4913477103605801E-8</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>5.4129356190608701E-10</c:v>
+                  <c:v>8.3264191209349899E-8</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>6.0296341797469096E-10</c:v>
+                  <c:v>9.1049288581031497E-8</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>5.6222679339298403E-10</c:v>
+                  <c:v>8.6416574325402399E-8</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>4.5207957754548799E-10</c:v>
+                  <c:v>7.1228262113146997E-8</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>4.5925559701541398E-10</c:v>
+                  <c:v>7.1674042631118694E-8</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>3.6105742678704099E-10</c:v>
+                  <c:v>5.8814106879375399E-8</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>2.4415170671318801E-10</c:v>
+                  <c:v>4.2028462983332902E-8</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>2.5964474180386499E-10</c:v>
+                  <c:v>4.4271922955657401E-8</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>3.1320516852857797E-10</c:v>
+                  <c:v>5.1739962039249402E-8</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>3.7411529757028501E-10</c:v>
+                  <c:v>6.1414011629415794E-8</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>4.7535055831767803E-10</c:v>
+                  <c:v>7.6211456307944803E-8</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>1.35726525047815E-8</c:v>
+                  <c:v>1.4754195766852299E-6</c:v>
                 </c:pt>
                 <c:pt idx="60" formatCode="General">
-                  <c:v>5.7102431065263301E-4</c:v>
+                  <c:v>1.5423120947055899E-2</c:v>
                 </c:pt>
                 <c:pt idx="61" formatCode="General">
-                  <c:v>2.27534202919115E-3</c:v>
+                  <c:v>5.1904084650772203E-3</c:v>
                 </c:pt>
                 <c:pt idx="62" formatCode="General">
-                  <c:v>9.900025355164409E-4</c:v>
+                  <c:v>4.2479273350382804E-3</c:v>
                 </c:pt>
                 <c:pt idx="63" formatCode="General">
-                  <c:v>2.9503740515731899E-4</c:v>
+                  <c:v>3.6689607626336899E-3</c:v>
                 </c:pt>
                 <c:pt idx="64" formatCode="General">
-                  <c:v>5.1401979061092601E-4</c:v>
+                  <c:v>3.8009525886131702E-3</c:v>
                 </c:pt>
                 <c:pt idx="65" formatCode="General">
-                  <c:v>1.0334830346720399E-3</c:v>
+                  <c:v>4.0915902838031598E-3</c:v>
                 </c:pt>
                 <c:pt idx="66" formatCode="General">
-                  <c:v>7.2361989397557304E-4</c:v>
+                  <c:v>4.1066535045521501E-3</c:v>
                 </c:pt>
                 <c:pt idx="67" formatCode="General">
-                  <c:v>5.0671515553957702E-4</c:v>
+                  <c:v>3.81052600834838E-3</c:v>
                 </c:pt>
                 <c:pt idx="68" formatCode="General">
-                  <c:v>3.6292172178298298E-4</c:v>
+                  <c:v>3.9552836608285503E-3</c:v>
                 </c:pt>
                 <c:pt idx="69" formatCode="General">
-                  <c:v>2.98156228743596E-4</c:v>
+                  <c:v>3.7380522520664501E-3</c:v>
                 </c:pt>
                 <c:pt idx="70" formatCode="General">
-                  <c:v>2.0862225839116699E-4</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>8.5098354639134103E-5</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>3.4809136627914099E-5</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>2.7082074992085E-5</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>1.30656730647897E-5</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>3.8862209671067402E-6</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>2.6515503817109999E-6</c:v>
+                  <c:v>3.38527038793886E-3</c:v>
+                </c:pt>
+                <c:pt idx="71" formatCode="General">
+                  <c:v>2.4202239275499301E-3</c:v>
+                </c:pt>
+                <c:pt idx="72" formatCode="General">
+                  <c:v>1.11520615110727E-3</c:v>
+                </c:pt>
+                <c:pt idx="73" formatCode="General">
+                  <c:v>8.9064617208336203E-4</c:v>
+                </c:pt>
+                <c:pt idx="74" formatCode="General">
+                  <c:v>4.7584114233522798E-4</c:v>
+                </c:pt>
+                <c:pt idx="75" formatCode="General">
+                  <c:v>1.7018734772214199E-4</c:v>
+                </c:pt>
+                <c:pt idx="76" formatCode="General">
+                  <c:v>1.24470880737367E-4</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>1.3810199356689E-6</c:v>
+                  <c:v>7.0911334416404696E-5</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>5.5071188114452805E-7</c:v>
+                  <c:v>3.24324587199272E-5</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>5.2540175849865201E-7</c:v>
+                  <c:v>3.1601412504950497E-5</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>6.0747217409804298E-7</c:v>
+                  <c:v>3.64598528387605E-5</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>4.4720960232561898E-7</c:v>
+                  <c:v>2.8204407565554602E-5</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>3.0172746386311302E-7</c:v>
+                  <c:v>2.0316057198426402E-5</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>2.35107426414113E-7</c:v>
+                  <c:v>1.6606812841669698E-5</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>2.2202552892917499E-7</c:v>
+                  <c:v>1.5706996456229699E-5</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>1.6952885446824599E-7</c:v>
+                  <c:v>1.2767304994691E-5</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>1.8897250739057999E-7</c:v>
+                  <c:v>1.38971609558558E-5</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>2.1399739126332401E-7</c:v>
+                  <c:v>1.5651695027523801E-5</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>1.3279940333071499E-7</c:v>
+                  <c:v>1.03792618030323E-5</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>1.00292044219874E-7</c:v>
+                  <c:v>8.0426144988607792E-6</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>1.2059315237547099E-7</c:v>
+                  <c:v>9.4898696381410604E-6</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>1.13534428409363E-7</c:v>
+                  <c:v>8.97841370194367E-6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5027,16 +5715,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>323851</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>178174</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
+      <xdr:rowOff>100292</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>66675</xdr:colOff>
+      <xdr:colOff>526116</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:rowOff>186017</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -5065,16 +5753,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>314324</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>168647</xdr:colOff>
       <xdr:row>45</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:rowOff>43142</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>95249</xdr:colOff>
+      <xdr:colOff>554690</xdr:colOff>
       <xdr:row>57</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:rowOff>62192</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -5103,16 +5791,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>314324</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>168647</xdr:colOff>
       <xdr:row>57</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:rowOff>90767</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>114299</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
+      <xdr:colOff>573740</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>5042</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -5464,8 +6152,10 @@
   <cols>
     <col min="1" max="1" width="15.28515625" customWidth="1"/>
     <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" customWidth="1"/>
+    <col min="4" max="4" width="12.28515625" customWidth="1"/>
     <col min="5" max="5" width="15.42578125" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
     <col min="20" max="20" width="12.7109375" customWidth="1"/>
     <col min="61" max="61" width="13.140625" customWidth="1"/>
     <col min="62" max="62" width="14" customWidth="1"/>
@@ -5759,280 +6449,280 @@
         <v>0</v>
       </c>
       <c r="B2" s="2">
-        <v>9.4170832457325001E-10</v>
+        <v>1.4221254009907999E-7</v>
       </c>
       <c r="C2" s="2">
-        <v>1.19225420553501E-9</v>
+        <v>1.79726955104284E-7</v>
       </c>
       <c r="D2" s="2">
-        <v>1.13718472474984E-9</v>
+        <v>1.69582018075944E-7</v>
       </c>
       <c r="E2" s="2">
-        <v>1.0151142238303101E-9</v>
+        <v>1.52839039433596E-7</v>
       </c>
       <c r="F2" s="2">
-        <v>6.4398678510234201E-10</v>
+        <v>1.0321196451396E-7</v>
       </c>
       <c r="G2" s="2">
-        <v>6.2715093817983104E-10</v>
+        <v>9.9320847969424001E-8</v>
       </c>
       <c r="H2" s="2">
-        <v>9.9990196305767197E-10</v>
+        <v>1.5051816349752101E-7</v>
       </c>
       <c r="I2" s="2">
-        <v>1.02326911631512E-9</v>
+        <v>1.54725410758714E-7</v>
       </c>
       <c r="J2" s="2">
-        <v>9.5971722737034707E-10</v>
+        <v>1.4647853697863599E-7</v>
       </c>
       <c r="K2" s="2">
-        <v>7.9877157460493596E-10</v>
+        <v>1.250864956627E-7</v>
       </c>
       <c r="L2" s="2">
-        <v>9.7700202241142105E-10</v>
+        <v>1.5005887693287601E-7</v>
       </c>
       <c r="M2" s="2">
-        <v>9.4746727011196394E-10</v>
+        <v>1.4259904240921899E-7</v>
       </c>
       <c r="N2" s="2">
-        <v>9.9179274251827295E-10</v>
+        <v>1.52001438766829E-7</v>
       </c>
       <c r="O2" s="2">
-        <v>9.0412029372403197E-10</v>
+        <v>1.3769639682143201E-7</v>
       </c>
       <c r="P2" s="2">
-        <v>6.1770763270172503E-10</v>
+        <v>1.00749518391823E-7</v>
       </c>
       <c r="Q2" s="2">
-        <v>6.6201536184373002E-10</v>
+        <v>1.05944141049072E-7</v>
       </c>
       <c r="R2" s="2">
-        <v>8.0323787221929904E-10</v>
+        <v>1.24184369088094E-7</v>
       </c>
       <c r="S2" s="2">
-        <v>8.9163950421949099E-10</v>
+        <v>1.37878724988046E-7</v>
       </c>
       <c r="T2" s="2">
-        <v>7.8059713555551002E-10</v>
+        <v>1.19886430033326E-7</v>
       </c>
       <c r="U2" s="2">
-        <v>8.1405890757249299E-10</v>
+        <v>1.2609225603872499E-7</v>
       </c>
       <c r="V2" s="2">
-        <v>7.7083428546008703E-10</v>
+        <v>1.20592636157517E-7</v>
       </c>
       <c r="W2" s="2">
-        <v>9.9394579461837903E-10</v>
+        <v>1.4862872126020399E-7</v>
       </c>
       <c r="X2" s="2">
-        <v>1.2167593713498799E-9</v>
+        <v>1.7464465475407299E-7</v>
       </c>
       <c r="Y2" s="2">
-        <v>9.9761659609293507E-10</v>
+        <v>1.49384516203063E-7</v>
       </c>
       <c r="Z2" s="2">
-        <v>8.6240978978739599E-10</v>
+        <v>1.31607155934079E-7</v>
       </c>
       <c r="AA2" s="2">
-        <v>6.2067528552950298E-10</v>
+        <v>9.9090210221863701E-8</v>
       </c>
       <c r="AB2" s="2">
-        <v>5.4594806038022402E-10</v>
+        <v>8.8754463725521903E-8</v>
       </c>
       <c r="AC2" s="2">
-        <v>5.2090447587157199E-10</v>
+        <v>8.4536834987216905E-8</v>
       </c>
       <c r="AD2" s="2">
-        <v>5.8306301614118296E-10</v>
+        <v>9.37925917280448E-8</v>
       </c>
       <c r="AE2" s="2">
-        <v>6.8948522561471099E-10</v>
+        <v>1.10005014672529E-7</v>
       </c>
       <c r="AF2" s="2">
-        <v>4.5233308144590302E-10</v>
+        <v>7.42269507867231E-8</v>
       </c>
       <c r="AG2" s="2">
-        <v>5.1388836432907001E-10</v>
+        <v>8.37489976291492E-8</v>
       </c>
       <c r="AH2" s="2">
-        <v>8.7150875242922001E-10</v>
+        <v>1.3456036196529701E-7</v>
       </c>
       <c r="AI2" s="2">
-        <v>8.5961704616773898E-10</v>
+        <v>1.3044573565671401E-7</v>
       </c>
       <c r="AJ2" s="2">
-        <v>6.8942732597906497E-10</v>
+        <v>1.0828443230519701E-7</v>
       </c>
       <c r="AK2" s="2">
-        <v>6.2702083736231303E-10</v>
+        <v>9.84825997732359E-8</v>
       </c>
       <c r="AL2" s="2">
-        <v>8.5293857979288797E-10</v>
+        <v>1.2803878825587399E-7</v>
       </c>
       <c r="AM2" s="2">
-        <v>8.1528735054230495E-10</v>
+        <v>1.2629784050930401E-7</v>
       </c>
       <c r="AN2" s="2">
-        <v>5.0022108606043999E-10</v>
+        <v>8.3491559530010094E-8</v>
       </c>
       <c r="AO2" s="2">
-        <v>4.6844564912095302E-10</v>
+        <v>7.7510850378197098E-8</v>
       </c>
       <c r="AP2" s="2">
-        <v>9.4067720518393391E-10</v>
+        <v>1.45550665327585E-7</v>
       </c>
       <c r="AQ2" s="2">
-        <v>6.5682430527547602E-10</v>
+        <v>1.03039015709554E-7</v>
       </c>
       <c r="AR2" s="2">
-        <v>6.3892786223280001E-10</v>
+        <v>1.0138129644085801E-7</v>
       </c>
       <c r="AS2" s="2">
-        <v>7.1708642457303E-10</v>
+        <v>1.11984058743973E-7</v>
       </c>
       <c r="AT2" s="2">
-        <v>4.5867702983181802E-10</v>
+        <v>7.5515919884758005E-8</v>
       </c>
       <c r="AU2" s="2">
-        <v>5.3868177925949697E-10</v>
+        <v>8.9569897468822199E-8</v>
       </c>
       <c r="AV2" s="2">
-        <v>6.1779634236488301E-10</v>
+        <v>9.9278824374308606E-8</v>
       </c>
       <c r="AW2" s="2">
-        <v>7.3499520574830097E-10</v>
+        <v>1.1433540602737001E-7</v>
       </c>
       <c r="AX2" s="2">
-        <v>9.4909688375402305E-10</v>
+        <v>1.45994317995278E-7</v>
       </c>
       <c r="AY2" s="2">
-        <v>8.8232007600894004E-10</v>
+        <v>1.3323298366791201E-7</v>
       </c>
       <c r="AZ2" s="2">
-        <v>8.3121502177750504E-10</v>
+        <v>1.27761173164764E-7</v>
       </c>
       <c r="BA2" s="2">
-        <v>7.5270898989416299E-10</v>
+        <v>1.18594503912163E-7</v>
       </c>
       <c r="BB2" s="2">
-        <v>8.2191583823346199E-10</v>
+        <v>1.2827286419484501E-7</v>
       </c>
       <c r="BC2" s="2">
-        <v>5.0678380596177797E-10</v>
+        <v>8.2552067113168302E-8</v>
       </c>
       <c r="BD2" s="2">
-        <v>3.2699546023203698E-10</v>
+        <v>5.6289250569251201E-8</v>
       </c>
       <c r="BE2" s="2">
-        <v>4.72004980013671E-10</v>
+        <v>8.0481383774328897E-8</v>
       </c>
       <c r="BF2" s="2">
-        <v>5.4989495226542702E-10</v>
+        <v>9.0839956727602702E-8</v>
       </c>
       <c r="BG2" s="2">
-        <v>6.6930170633289299E-10</v>
+        <v>1.0987121629035801E-7</v>
       </c>
       <c r="BH2" s="2">
-        <v>1.0489946937872801E-9</v>
+        <v>1.6818201192618799E-7</v>
       </c>
       <c r="BI2" s="2">
-        <v>2.3911052353288801E-8</v>
-      </c>
-      <c r="BJ2">
-        <v>8.4256581576265999E-4</v>
+        <v>2.59925867337766E-6</v>
+      </c>
+      <c r="BJ2" s="10">
+        <v>2.2757340169528399E-2</v>
       </c>
       <c r="BK2">
-        <v>3.0194890839779602E-3</v>
+        <v>6.88792344191058E-3</v>
       </c>
       <c r="BL2">
-        <v>1.3419280710164001E-3</v>
+        <v>5.7579781162764004E-3</v>
       </c>
       <c r="BM2">
-        <v>4.3902523980032999E-4</v>
+        <v>5.4595327590182402E-3</v>
       </c>
       <c r="BN2">
-        <v>6.5939852060204699E-4</v>
+        <v>4.8759650107001798E-3</v>
       </c>
       <c r="BO2">
-        <v>1.3813185597794501E-3</v>
+        <v>5.4686815441540304E-3</v>
       </c>
       <c r="BP2">
-        <v>9.8204166941528396E-4</v>
+        <v>5.5732365802783701E-3</v>
       </c>
       <c r="BQ2">
-        <v>6.8230783756815302E-4</v>
+        <v>5.13099269333694E-3</v>
       </c>
       <c r="BR2">
-        <v>4.8825608108944398E-4</v>
+        <v>5.3212337093761601E-3</v>
       </c>
       <c r="BS2">
-        <v>4.0077653523385402E-4</v>
+        <v>5.0246263053807796E-3</v>
       </c>
       <c r="BT2">
-        <v>2.8406229446980902E-4</v>
+        <v>4.6094203043980297E-3</v>
       </c>
       <c r="BU2">
-        <v>1.15579019054127E-4</v>
-      </c>
-      <c r="BV2" s="2">
-        <v>4.8066690553333703E-5</v>
-      </c>
-      <c r="BW2" s="2">
-        <v>3.9194224418457197E-5</v>
-      </c>
-      <c r="BX2" s="2">
-        <v>2.2204912325750299E-5</v>
-      </c>
-      <c r="BY2" s="2">
-        <v>5.7209591914661297E-6</v>
-      </c>
-      <c r="BZ2" s="2">
-        <v>4.6235635463227896E-6</v>
-      </c>
-      <c r="CA2" s="2">
-        <v>2.0442095213971602E-6</v>
+        <v>3.2871035946504899E-3</v>
+      </c>
+      <c r="BV2">
+        <v>1.53994824810323E-3</v>
+      </c>
+      <c r="BW2">
+        <v>1.2889775231266999E-3</v>
+      </c>
+      <c r="BX2">
+        <v>8.0868477222856099E-4</v>
+      </c>
+      <c r="BY2">
+        <v>2.5053512897688302E-4</v>
+      </c>
+      <c r="BZ2">
+        <v>2.17042463423721E-4</v>
+      </c>
+      <c r="CA2">
+        <v>1.0496417991406E-4</v>
       </c>
       <c r="CB2" s="2">
-        <v>8.4608754407049798E-7</v>
+        <v>4.98276871901227E-5</v>
       </c>
       <c r="CC2" s="2">
-        <v>7.9548858694861903E-7</v>
+        <v>4.7846362469734101E-5</v>
       </c>
       <c r="CD2" s="2">
-        <v>9.2995385842568605E-7</v>
+        <v>5.58148706582288E-5</v>
       </c>
       <c r="CE2" s="2">
-        <v>7.1353611262290904E-7</v>
+        <v>4.5000964263210298E-5</v>
       </c>
       <c r="CF2" s="2">
-        <v>4.4749196250294002E-7</v>
+        <v>3.0130741794009601E-5</v>
       </c>
       <c r="CG2" s="2">
-        <v>2.97598488557786E-7</v>
+        <v>2.1020868956811798E-5</v>
       </c>
       <c r="CH2" s="2">
-        <v>2.91656407736742E-7</v>
+        <v>2.0632970383662501E-5</v>
       </c>
       <c r="CI2" s="2">
-        <v>2.38278498467708E-7</v>
+        <v>1.7944875951429599E-5</v>
       </c>
       <c r="CJ2" s="2">
-        <v>2.7142588960351998E-7</v>
+        <v>1.99608362478804E-5</v>
       </c>
       <c r="CK2" s="2">
-        <v>2.8845317308508E-7</v>
+        <v>2.1097365103920101E-5</v>
       </c>
       <c r="CL2" s="2">
-        <v>1.7803150855957199E-7</v>
+        <v>1.39144874919424E-5</v>
       </c>
       <c r="CM2" s="2">
-        <v>1.3568315097894001E-7</v>
+        <v>1.08806963286294E-5</v>
       </c>
       <c r="CN2" s="2">
-        <v>1.86896842999386E-7</v>
+        <v>1.4707523941653399E-5</v>
       </c>
       <c r="CO2" s="2">
-        <v>1.5120622219659301E-7</v>
+        <v>1.19575360197737E-5</v>
       </c>
     </row>
     <row r="3" spans="1:97" x14ac:dyDescent="0.25">
@@ -6040,280 +6730,280 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>6.7817983640293597E-10</v>
+        <v>1.0241565744345101E-7</v>
       </c>
       <c r="C3" s="2">
-        <v>7.9935488811814302E-10</v>
+        <v>1.20499151459588E-7</v>
       </c>
       <c r="D3" s="2">
-        <v>8.0473361940703399E-10</v>
+        <v>1.20005438184596E-7</v>
       </c>
       <c r="E3" s="2">
-        <v>7.2252814219493303E-10</v>
+        <v>1.08786286926953E-7</v>
       </c>
       <c r="F3" s="2">
-        <v>4.4567946577085499E-10</v>
+        <v>7.1429188097304793E-8</v>
       </c>
       <c r="G3" s="2">
-        <v>4.6111146412390699E-10</v>
+        <v>7.30254534228644E-8</v>
       </c>
       <c r="H3" s="2">
-        <v>6.9556006144983501E-10</v>
+        <v>1.04704687978662E-7</v>
       </c>
       <c r="I3" s="2">
-        <v>6.7940669377925398E-10</v>
+        <v>1.02731019720165E-7</v>
       </c>
       <c r="J3" s="2">
-        <v>6.4767005517130501E-10</v>
+        <v>9.8851786152673197E-8</v>
       </c>
       <c r="K3" s="2">
-        <v>5.4184663617276897E-10</v>
+        <v>8.4852414708764497E-8</v>
       </c>
       <c r="L3" s="2">
-        <v>6.2835086765185102E-10</v>
+        <v>9.6509140572479604E-8</v>
       </c>
       <c r="M3" s="2">
-        <v>7.4436162291078E-10</v>
+        <v>1.1203052388438301E-7</v>
       </c>
       <c r="N3" s="2">
-        <v>6.45184550477534E-10</v>
+        <v>9.8880517814838898E-8</v>
       </c>
       <c r="O3" s="2">
-        <v>6.5859411579469405E-10</v>
+        <v>1.00303065136692E-7</v>
       </c>
       <c r="P3" s="2">
-        <v>4.0783672234896999E-10</v>
+        <v>6.65190960647415E-8</v>
       </c>
       <c r="Q3" s="2">
-        <v>4.66962373632692E-10</v>
+        <v>7.4729274315264904E-8</v>
       </c>
       <c r="R3" s="2">
-        <v>5.92647323868018E-10</v>
+        <v>9.1626075600631999E-8</v>
       </c>
       <c r="S3" s="2">
-        <v>5.8876469747462296E-10</v>
+        <v>9.1043662179332501E-8</v>
       </c>
       <c r="T3" s="2">
-        <v>5.88856603044077E-10</v>
+        <v>9.0438348701767694E-8</v>
       </c>
       <c r="U3" s="2">
-        <v>5.1738292916028E-10</v>
+        <v>8.0139140013971602E-8</v>
       </c>
       <c r="V3" s="2">
-        <v>5.1529120463564605E-10</v>
+        <v>8.0614375783670403E-8</v>
       </c>
       <c r="W3" s="2">
-        <v>6.6814915093842095E-10</v>
+        <v>9.9911035846152306E-8</v>
       </c>
       <c r="X3" s="2">
-        <v>8.8406100913321904E-10</v>
+        <v>1.2689158872093E-7</v>
       </c>
       <c r="Y3" s="2">
-        <v>6.6604720288510995E-10</v>
+        <v>9.9734847598926806E-8</v>
       </c>
       <c r="Z3" s="2">
-        <v>5.8611970716859301E-10</v>
+        <v>8.9444193016331499E-8</v>
       </c>
       <c r="AA3" s="2">
-        <v>4.3424020476832302E-10</v>
+        <v>6.9326029535019303E-8</v>
       </c>
       <c r="AB3" s="2">
-        <v>3.8182657244080302E-10</v>
+        <v>6.2073327359061195E-8</v>
       </c>
       <c r="AC3" s="2">
-        <v>3.7292213053298599E-10</v>
+        <v>6.0520993909596605E-8</v>
       </c>
       <c r="AD3" s="2">
-        <v>4.0947433337382098E-10</v>
+        <v>6.5868796186162205E-8</v>
       </c>
       <c r="AE3" s="2">
-        <v>4.2537444364903198E-10</v>
+        <v>6.7867040767186004E-8</v>
       </c>
       <c r="AF3" s="2">
-        <v>3.3617646604093302E-10</v>
+        <v>5.5165883337354401E-8</v>
       </c>
       <c r="AG3" s="2">
-        <v>3.6202863176049598E-10</v>
+        <v>5.9000236484766003E-8</v>
       </c>
       <c r="AH3" s="2">
-        <v>5.5160123399840004E-10</v>
+        <v>8.5166857477847597E-8</v>
       </c>
       <c r="AI3" s="2">
-        <v>6.0404134311816401E-10</v>
+        <v>9.1662464954226799E-8</v>
       </c>
       <c r="AJ3" s="2">
-        <v>4.5900594760520299E-10</v>
+        <v>7.20934558107596E-8</v>
       </c>
       <c r="AK3" s="2">
-        <v>4.6460794079042198E-10</v>
+        <v>7.2973329046067995E-8</v>
       </c>
       <c r="AL3" s="2">
-        <v>6.6496900461993103E-10</v>
+        <v>9.9821754575454596E-8</v>
       </c>
       <c r="AM3" s="2">
-        <v>5.6304335255230795E-10</v>
+        <v>8.7222203919932196E-8</v>
       </c>
       <c r="AN3" s="2">
-        <v>3.3192733722912098E-10</v>
+        <v>5.5401764956497602E-8</v>
       </c>
       <c r="AO3" s="2">
-        <v>3.3981300122528198E-10</v>
+        <v>5.6226789050408003E-8</v>
       </c>
       <c r="AP3" s="2">
-        <v>5.9749891916897197E-10</v>
+        <v>9.2450805376652304E-8</v>
       </c>
       <c r="AQ3" s="2">
-        <v>4.9117454685511605E-10</v>
+        <v>7.7052784807964101E-8</v>
       </c>
       <c r="AR3" s="2">
-        <v>4.3201938664700999E-10</v>
+        <v>6.8550282581515004E-8</v>
       </c>
       <c r="AS3" s="2">
-        <v>4.9142552613458E-10</v>
+        <v>7.6743643584538195E-8</v>
       </c>
       <c r="AT3" s="2">
-        <v>3.36586100920068E-10</v>
+        <v>5.5415046706262998E-8</v>
       </c>
       <c r="AU3" s="2">
-        <v>3.2487796769969299E-10</v>
+        <v>5.4019436663800003E-8</v>
       </c>
       <c r="AV3" s="2">
-        <v>4.3302363931941802E-10</v>
+        <v>6.9586164386871801E-8</v>
       </c>
       <c r="AW3" s="2">
-        <v>4.9935639501594296E-10</v>
+        <v>7.7679576315849496E-8</v>
       </c>
       <c r="AX3" s="2">
-        <v>5.4693488119704999E-10</v>
+        <v>8.4131964117135899E-8</v>
       </c>
       <c r="AY3" s="2">
-        <v>6.2229837965693897E-10</v>
+        <v>9.3968925913969705E-8</v>
       </c>
       <c r="AZ3" s="2">
-        <v>5.72337455465218E-10</v>
+        <v>8.7970624737456199E-8</v>
       </c>
       <c r="BA3" s="2">
-        <v>4.6951422905553096E-10</v>
+        <v>7.3975211962877299E-8</v>
       </c>
       <c r="BB3" s="2">
-        <v>4.7835593819346598E-10</v>
+        <v>7.4654950597264206E-8</v>
       </c>
       <c r="BC3" s="2">
-        <v>3.7062344732674202E-10</v>
+        <v>6.0372354715777496E-8</v>
       </c>
       <c r="BD3" s="2">
-        <v>2.4640797211936901E-10</v>
+        <v>4.2416858249319797E-8</v>
       </c>
       <c r="BE3" s="2">
-        <v>2.5879797023507401E-10</v>
+        <v>4.4127540268418999E-8</v>
       </c>
       <c r="BF3" s="2">
-        <v>3.2574195123283501E-10</v>
+        <v>5.3810977227716901E-8</v>
       </c>
       <c r="BG3" s="2">
-        <v>3.87628032659233E-10</v>
+        <v>6.3632234929052404E-8</v>
       </c>
       <c r="BH3" s="2">
-        <v>4.89366799657478E-10</v>
+        <v>7.8458636089864999E-8</v>
       </c>
       <c r="BI3" s="2">
-        <v>1.38580466497013E-8</v>
-      </c>
-      <c r="BJ3">
-        <v>5.5810267175125205E-4</v>
+        <v>1.5064434394438E-6</v>
+      </c>
+      <c r="BJ3" s="10">
+        <v>1.5074113040056999E-2</v>
       </c>
       <c r="BK3">
-        <v>2.30725901968859E-3</v>
+        <v>5.2632160762136997E-3</v>
       </c>
       <c r="BL3">
-        <v>1.00295106012561E-3</v>
+        <v>4.3034871843328102E-3</v>
       </c>
       <c r="BM3">
-        <v>3.0019692886353901E-4</v>
+        <v>3.73312242376734E-3</v>
       </c>
       <c r="BN3">
-        <v>5.1861207800330098E-4</v>
+        <v>3.8349105547707601E-3</v>
       </c>
       <c r="BO3">
-        <v>1.0531266020267699E-3</v>
+        <v>4.1693597551748099E-3</v>
       </c>
       <c r="BP3">
-        <v>7.1698376637975103E-4</v>
+        <v>4.0689924661150003E-3</v>
       </c>
       <c r="BQ3">
-        <v>5.1341501153308496E-4</v>
+        <v>3.8609092961429401E-3</v>
       </c>
       <c r="BR3">
-        <v>3.6351370550483997E-4</v>
+        <v>3.9617353648852298E-3</v>
       </c>
       <c r="BS3">
-        <v>3.0147754661757399E-4</v>
+        <v>3.7796923673478599E-3</v>
       </c>
       <c r="BT3">
-        <v>2.1045785151038799E-4</v>
-      </c>
-      <c r="BU3" s="2">
-        <v>8.5382289286336493E-5</v>
-      </c>
-      <c r="BV3" s="2">
-        <v>3.5339869466431098E-5</v>
-      </c>
-      <c r="BW3" s="2">
-        <v>2.7627215109462799E-5</v>
-      </c>
-      <c r="BX3" s="2">
-        <v>1.37545459257828E-5</v>
-      </c>
-      <c r="BY3" s="2">
-        <v>3.9840848125274297E-6</v>
-      </c>
-      <c r="BZ3" s="2">
-        <v>2.6842380066374601E-6</v>
+        <v>3.4150561791017799E-3</v>
+      </c>
+      <c r="BU3">
+        <v>2.4282991180632702E-3</v>
+      </c>
+      <c r="BV3">
+        <v>1.13220963305243E-3</v>
+      </c>
+      <c r="BW3">
+        <v>9.0857415429634804E-4</v>
+      </c>
+      <c r="BX3">
+        <v>5.0092932934170495E-4</v>
+      </c>
+      <c r="BY3">
+        <v>1.7447305057741801E-4</v>
+      </c>
+      <c r="BZ3">
+        <v>1.2600532544730899E-4</v>
       </c>
       <c r="CA3" s="2">
-        <v>1.4058412218177401E-6</v>
+        <v>7.2185834863316203E-5</v>
       </c>
       <c r="CB3" s="2">
-        <v>5.6447780454141204E-7</v>
+        <v>3.3243159845828698E-5</v>
       </c>
       <c r="CC3" s="2">
-        <v>5.4522666378771696E-7</v>
+        <v>3.2793823835698597E-5</v>
       </c>
       <c r="CD3" s="2">
-        <v>6.09978026661199E-7</v>
+        <v>3.6610251523688897E-5</v>
       </c>
       <c r="CE3" s="2">
-        <v>4.60290903372103E-7</v>
+        <v>2.9029412986223601E-5</v>
       </c>
       <c r="CF3" s="2">
-        <v>3.0123017056390899E-7</v>
+        <v>2.0282573208857299E-5</v>
       </c>
       <c r="CG3" s="2">
-        <v>2.3196495809394001E-7</v>
+        <v>1.6384844595069299E-5</v>
       </c>
       <c r="CH3" s="2">
-        <v>2.23014422514708E-7</v>
+        <v>1.57769548440178E-5</v>
       </c>
       <c r="CI3" s="2">
-        <v>1.72637766353315E-7</v>
+        <v>1.30014387435252E-5</v>
       </c>
       <c r="CJ3" s="2">
-        <v>1.9534509780769699E-7</v>
+        <v>1.43658053952108E-5</v>
       </c>
       <c r="CK3" s="2">
-        <v>2.1541480276719E-7</v>
+        <v>1.5755364013596901E-5</v>
       </c>
       <c r="CL3" s="2">
-        <v>1.33715456593602E-7</v>
+        <v>1.04508581839459E-5</v>
       </c>
       <c r="CM3" s="2">
-        <v>1.0094948792846299E-7</v>
+        <v>8.0953361912696808E-6</v>
       </c>
       <c r="CN3" s="2">
-        <v>1.2465689326174701E-7</v>
+        <v>9.8096587014311299E-6</v>
       </c>
       <c r="CO3" s="2">
-        <v>1.1480211508073799E-7</v>
+        <v>9.0786636044787495E-6</v>
       </c>
     </row>
     <row r="4" spans="1:97" x14ac:dyDescent="0.25">
@@ -6321,280 +7011,280 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>6.6705963235866703E-10</v>
+        <v>1.0073633442779E-7</v>
       </c>
       <c r="C4" s="2">
-        <v>7.8287815236245401E-10</v>
+        <v>1.18015357706683E-7</v>
       </c>
       <c r="D4" s="2">
-        <v>7.8143387235638396E-10</v>
+        <v>1.16530876805227E-7</v>
       </c>
       <c r="E4" s="2">
-        <v>7.0875576954331898E-10</v>
+        <v>1.0671267180346699E-7</v>
       </c>
       <c r="F4" s="2">
-        <v>4.2747369092617503E-10</v>
+        <v>6.8511342838640803E-8</v>
       </c>
       <c r="G4" s="2">
-        <v>4.45093909203132E-10</v>
+        <v>7.0488779968203097E-8</v>
       </c>
       <c r="H4" s="2">
-        <v>6.6392990013645499E-10</v>
+        <v>9.9943307395675201E-8</v>
       </c>
       <c r="I4" s="2">
-        <v>6.5978128215744202E-10</v>
+        <v>9.9763520923234002E-8</v>
       </c>
       <c r="J4" s="2">
-        <v>6.2250654971797597E-10</v>
+        <v>9.5011161685906004E-8</v>
       </c>
       <c r="K4" s="2">
-        <v>5.3286742621083799E-10</v>
+        <v>8.3446283164622004E-8</v>
       </c>
       <c r="L4" s="2">
-        <v>6.0535869958787201E-10</v>
+        <v>9.29777467387017E-8</v>
       </c>
       <c r="M4" s="2">
-        <v>7.3707415853799905E-10</v>
+        <v>1.10933720359415E-7</v>
       </c>
       <c r="N4" s="2">
-        <v>6.3212548690507896E-10</v>
+        <v>9.6879095171269695E-8</v>
       </c>
       <c r="O4" s="2">
-        <v>6.3424407303283705E-10</v>
+        <v>9.6594583892903297E-8</v>
       </c>
       <c r="P4" s="2">
-        <v>4.0384717270957802E-10</v>
+        <v>6.5868391454465701E-8</v>
       </c>
       <c r="Q4" s="2">
-        <v>4.5209966933268698E-10</v>
+        <v>7.2350754825156606E-8</v>
       </c>
       <c r="R4" s="2">
-        <v>5.8212743970692898E-10</v>
+        <v>8.9999651819504605E-8</v>
       </c>
       <c r="S4" s="2">
-        <v>5.7397606382619397E-10</v>
+        <v>8.8756820982546494E-8</v>
       </c>
       <c r="T4" s="2">
-        <v>5.8515172826811804E-10</v>
+        <v>8.9869343015544797E-8</v>
       </c>
       <c r="U4" s="2">
-        <v>5.11387904601465E-10</v>
+        <v>7.9210550984000096E-8</v>
       </c>
       <c r="V4" s="2">
-        <v>4.9604013721892498E-10</v>
+        <v>7.7602655868289506E-8</v>
       </c>
       <c r="W4" s="2">
-        <v>6.6922468618957803E-10</v>
+        <v>1.00071864968304E-7</v>
       </c>
       <c r="X4" s="2">
-        <v>8.5683742196982795E-10</v>
+        <v>1.2298411605744001E-7</v>
       </c>
       <c r="Y4" s="2">
-        <v>6.48865689616417E-10</v>
+        <v>9.7162063567462706E-8</v>
       </c>
       <c r="Z4" s="2">
-        <v>5.8022196753551605E-10</v>
+        <v>8.8544174547710997E-8</v>
       </c>
       <c r="AA4" s="2">
-        <v>4.2592079278639002E-10</v>
+        <v>6.7997843442912401E-8</v>
       </c>
       <c r="AB4" s="2">
-        <v>3.7585111632660001E-10</v>
+        <v>6.1101900878412694E-8</v>
       </c>
       <c r="AC4" s="2">
-        <v>3.6676338273875602E-10</v>
+        <v>5.95214996260397E-8</v>
       </c>
       <c r="AD4" s="2">
-        <v>3.9646036096304999E-10</v>
+        <v>6.3775344592046203E-8</v>
       </c>
       <c r="AE4" s="2">
-        <v>4.1509363568013599E-10</v>
+        <v>6.6226772943665902E-8</v>
       </c>
       <c r="AF4" s="2">
-        <v>3.32905053105935E-10</v>
+        <v>5.4629051040995798E-8</v>
       </c>
       <c r="AG4" s="2">
-        <v>3.5559226663422601E-10</v>
+        <v>5.7951294409898098E-8</v>
       </c>
       <c r="AH4" s="2">
-        <v>5.4487477046016601E-10</v>
+        <v>8.41282960556246E-8</v>
       </c>
       <c r="AI4" s="2">
-        <v>5.8966330620128902E-10</v>
+        <v>8.9480617106329296E-8</v>
       </c>
       <c r="AJ4" s="2">
-        <v>4.40987573149627E-10</v>
+        <v>6.9263412127430206E-8</v>
       </c>
       <c r="AK4" s="2">
-        <v>4.5915625771288198E-10</v>
+        <v>7.2117064164911005E-8</v>
       </c>
       <c r="AL4" s="2">
-        <v>6.3493447019437199E-10</v>
+        <v>9.5313123490926E-8</v>
       </c>
       <c r="AM4" s="2">
-        <v>5.5045012158756103E-10</v>
+        <v>8.5271360606545198E-8</v>
       </c>
       <c r="AN4" s="2">
-        <v>3.1403445702283099E-10</v>
+        <v>5.2415276552998997E-8</v>
       </c>
       <c r="AO4" s="2">
-        <v>3.3049676507131203E-10</v>
+        <v>5.4685288157373297E-8</v>
       </c>
       <c r="AP4" s="2">
-        <v>5.7387604940369601E-10</v>
+        <v>8.8795646739425097E-8</v>
       </c>
       <c r="AQ4" s="2">
-        <v>4.8591189854669703E-10</v>
+        <v>7.6227209236170099E-8</v>
       </c>
       <c r="AR4" s="2">
-        <v>4.2364331779199299E-10</v>
+        <v>6.7221217486965405E-8</v>
       </c>
       <c r="AS4" s="2">
-        <v>4.7921129578899002E-10</v>
+        <v>7.4836203919844605E-8</v>
       </c>
       <c r="AT4" s="2">
-        <v>3.2110161961366301E-10</v>
+        <v>5.2865704198383603E-8</v>
       </c>
       <c r="AU4" s="2">
-        <v>3.1234882234302598E-10</v>
+        <v>5.1936139422548101E-8</v>
       </c>
       <c r="AV4" s="2">
-        <v>4.2005611076522498E-10</v>
+        <v>6.7502304541728903E-8</v>
       </c>
       <c r="AW4" s="2">
-        <v>4.8157476699739597E-10</v>
+        <v>7.4913477103605801E-8</v>
       </c>
       <c r="AX4" s="2">
-        <v>5.4129356190608701E-10</v>
+        <v>8.3264191209349899E-8</v>
       </c>
       <c r="AY4" s="2">
-        <v>6.0296341797469096E-10</v>
+        <v>9.1049288581031497E-8</v>
       </c>
       <c r="AZ4" s="2">
-        <v>5.6222679339298403E-10</v>
+        <v>8.6416574325402399E-8</v>
       </c>
       <c r="BA4" s="2">
-        <v>4.5207957754548799E-10</v>
+        <v>7.1228262113146997E-8</v>
       </c>
       <c r="BB4" s="2">
-        <v>4.5925559701541398E-10</v>
+        <v>7.1674042631118694E-8</v>
       </c>
       <c r="BC4" s="2">
-        <v>3.6105742678704099E-10</v>
+        <v>5.8814106879375399E-8</v>
       </c>
       <c r="BD4" s="2">
-        <v>2.4415170671318801E-10</v>
+        <v>4.2028462983332902E-8</v>
       </c>
       <c r="BE4" s="2">
-        <v>2.5964474180386499E-10</v>
+        <v>4.4271922955657401E-8</v>
       </c>
       <c r="BF4" s="2">
-        <v>3.1320516852857797E-10</v>
+        <v>5.1739962039249402E-8</v>
       </c>
       <c r="BG4" s="2">
-        <v>3.7411529757028501E-10</v>
+        <v>6.1414011629415794E-8</v>
       </c>
       <c r="BH4" s="2">
-        <v>4.7535055831767803E-10</v>
+        <v>7.6211456307944803E-8</v>
       </c>
       <c r="BI4" s="2">
-        <v>1.35726525047815E-8</v>
-      </c>
-      <c r="BJ4">
-        <v>5.7102431065263301E-4</v>
+        <v>1.4754195766852299E-6</v>
+      </c>
+      <c r="BJ4" s="10">
+        <v>1.5423120947055899E-2</v>
       </c>
       <c r="BK4">
-        <v>2.27534202919115E-3</v>
+        <v>5.1904084650772203E-3</v>
       </c>
       <c r="BL4">
-        <v>9.900025355164409E-4</v>
+        <v>4.2479273350382804E-3</v>
       </c>
       <c r="BM4">
-        <v>2.9503740515731899E-4</v>
+        <v>3.6689607626336899E-3</v>
       </c>
       <c r="BN4">
-        <v>5.1401979061092601E-4</v>
+        <v>3.8009525886131702E-3</v>
       </c>
       <c r="BO4">
-        <v>1.0334830346720399E-3</v>
+        <v>4.0915902838031598E-3</v>
       </c>
       <c r="BP4">
-        <v>7.2361989397557304E-4</v>
+        <v>4.1066535045521501E-3</v>
       </c>
       <c r="BQ4">
-        <v>5.0671515553957702E-4</v>
+        <v>3.81052600834838E-3</v>
       </c>
       <c r="BR4">
-        <v>3.6292172178298298E-4</v>
+        <v>3.9552836608285503E-3</v>
       </c>
       <c r="BS4">
-        <v>2.98156228743596E-4</v>
+        <v>3.7380522520664501E-3</v>
       </c>
       <c r="BT4">
-        <v>2.0862225839116699E-4</v>
-      </c>
-      <c r="BU4" s="2">
-        <v>8.5098354639134103E-5</v>
-      </c>
-      <c r="BV4" s="2">
-        <v>3.4809136627914099E-5</v>
-      </c>
-      <c r="BW4" s="2">
-        <v>2.7082074992085E-5</v>
-      </c>
-      <c r="BX4" s="2">
-        <v>1.30656730647897E-5</v>
-      </c>
-      <c r="BY4" s="2">
-        <v>3.8862209671067402E-6</v>
-      </c>
-      <c r="BZ4" s="2">
-        <v>2.6515503817109999E-6</v>
+        <v>3.38527038793886E-3</v>
+      </c>
+      <c r="BU4">
+        <v>2.4202239275499301E-3</v>
+      </c>
+      <c r="BV4">
+        <v>1.11520615110727E-3</v>
+      </c>
+      <c r="BW4">
+        <v>8.9064617208336203E-4</v>
+      </c>
+      <c r="BX4">
+        <v>4.7584114233522798E-4</v>
+      </c>
+      <c r="BY4">
+        <v>1.7018734772214199E-4</v>
+      </c>
+      <c r="BZ4">
+        <v>1.24470880737367E-4</v>
       </c>
       <c r="CA4" s="2">
-        <v>1.3810199356689E-6</v>
+        <v>7.0911334416404696E-5</v>
       </c>
       <c r="CB4" s="2">
-        <v>5.5071188114452805E-7</v>
+        <v>3.24324587199272E-5</v>
       </c>
       <c r="CC4" s="2">
-        <v>5.2540175849865201E-7</v>
+        <v>3.1601412504950497E-5</v>
       </c>
       <c r="CD4" s="2">
-        <v>6.0747217409804298E-7</v>
+        <v>3.64598528387605E-5</v>
       </c>
       <c r="CE4" s="2">
-        <v>4.4720960232561898E-7</v>
+        <v>2.8204407565554602E-5</v>
       </c>
       <c r="CF4" s="2">
-        <v>3.0172746386311302E-7</v>
+        <v>2.0316057198426402E-5</v>
       </c>
       <c r="CG4" s="2">
-        <v>2.35107426414113E-7</v>
+        <v>1.6606812841669698E-5</v>
       </c>
       <c r="CH4" s="2">
-        <v>2.2202552892917499E-7</v>
+        <v>1.5706996456229699E-5</v>
       </c>
       <c r="CI4" s="2">
-        <v>1.6952885446824599E-7</v>
+        <v>1.2767304994691E-5</v>
       </c>
       <c r="CJ4" s="2">
-        <v>1.8897250739057999E-7</v>
+        <v>1.38971609558558E-5</v>
       </c>
       <c r="CK4" s="2">
-        <v>2.1399739126332401E-7</v>
+        <v>1.5651695027523801E-5</v>
       </c>
       <c r="CL4" s="2">
-        <v>1.3279940333071499E-7</v>
+        <v>1.03792618030323E-5</v>
       </c>
       <c r="CM4" s="2">
-        <v>1.00292044219874E-7</v>
+        <v>8.0426144988607792E-6</v>
       </c>
       <c r="CN4" s="2">
-        <v>1.2059315237547099E-7</v>
+        <v>9.4898696381410604E-6</v>
       </c>
       <c r="CO4" s="2">
-        <v>1.13534428409363E-7</v>
+        <v>8.97841370194367E-6</v>
       </c>
     </row>
     <row r="5" spans="1:97" x14ac:dyDescent="0.25">
@@ -6781,7 +7471,7 @@
       <c r="BI5">
         <v>0</v>
       </c>
-      <c r="BJ5">
+      <c r="BJ5" s="10">
         <v>0</v>
       </c>
       <c r="BK5">
@@ -7062,8 +7752,8 @@
       <c r="BI6">
         <v>0</v>
       </c>
-      <c r="BJ6">
-        <v>0</v>
+      <c r="BJ6" s="10">
+        <v>29</v>
       </c>
       <c r="BK6">
         <v>0</v>
@@ -7343,35 +8033,35 @@
       <c r="BI7">
         <v>0</v>
       </c>
-      <c r="BJ7">
-        <v>0</v>
+      <c r="BJ7" s="10">
+        <v>474</v>
       </c>
       <c r="BK7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BL7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BM7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BN7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BO7">
         <v>0</v>
       </c>
       <c r="BP7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR7">
         <v>0</v>
       </c>
       <c r="BS7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BT7">
         <v>0</v>
@@ -7624,50 +8314,50 @@
       <c r="BI8">
         <v>0</v>
       </c>
-      <c r="BJ8">
-        <v>8</v>
+      <c r="BJ8" s="10">
+        <v>5962</v>
       </c>
       <c r="BK8">
-        <v>26</v>
+        <v>322</v>
       </c>
       <c r="BL8">
+        <v>201</v>
+      </c>
+      <c r="BM8">
+        <v>145</v>
+      </c>
+      <c r="BN8">
+        <v>117</v>
+      </c>
+      <c r="BO8">
+        <v>185</v>
+      </c>
+      <c r="BP8">
+        <v>168</v>
+      </c>
+      <c r="BQ8">
+        <v>121</v>
+      </c>
+      <c r="BR8">
+        <v>159</v>
+      </c>
+      <c r="BS8">
+        <v>126</v>
+      </c>
+      <c r="BT8">
+        <v>103</v>
+      </c>
+      <c r="BU8">
+        <v>30</v>
+      </c>
+      <c r="BV8">
+        <v>4</v>
+      </c>
+      <c r="BW8">
+        <v>3</v>
+      </c>
+      <c r="BX8">
         <v>1</v>
-      </c>
-      <c r="BM8">
-        <v>0</v>
-      </c>
-      <c r="BN8">
-        <v>0</v>
-      </c>
-      <c r="BO8">
-        <v>0</v>
-      </c>
-      <c r="BP8">
-        <v>2</v>
-      </c>
-      <c r="BQ8">
-        <v>0</v>
-      </c>
-      <c r="BR8">
-        <v>0</v>
-      </c>
-      <c r="BS8">
-        <v>0</v>
-      </c>
-      <c r="BT8">
-        <v>0</v>
-      </c>
-      <c r="BU8">
-        <v>0</v>
-      </c>
-      <c r="BV8">
-        <v>0</v>
-      </c>
-      <c r="BW8">
-        <v>0</v>
-      </c>
-      <c r="BX8">
-        <v>0</v>
       </c>
       <c r="BY8">
         <v>0</v>
@@ -7905,53 +8595,53 @@
       <c r="BI9">
         <v>0</v>
       </c>
-      <c r="BJ9">
-        <v>163</v>
+      <c r="BJ9" s="10">
+        <v>27015</v>
       </c>
       <c r="BK9">
-        <v>1832</v>
+        <v>14471</v>
       </c>
       <c r="BL9">
-        <v>167</v>
+        <v>9597</v>
       </c>
       <c r="BM9">
-        <v>6</v>
+        <v>6486</v>
       </c>
       <c r="BN9">
-        <v>8</v>
+        <v>7142</v>
       </c>
       <c r="BO9">
-        <v>194</v>
+        <v>8264</v>
       </c>
       <c r="BP9">
-        <v>56</v>
+        <v>8195</v>
       </c>
       <c r="BQ9">
-        <v>19</v>
+        <v>7351</v>
       </c>
       <c r="BR9">
-        <v>7</v>
+        <v>7366</v>
       </c>
       <c r="BS9">
-        <v>7</v>
+        <v>6939</v>
       </c>
       <c r="BT9">
-        <v>0</v>
+        <v>5294</v>
       </c>
       <c r="BU9">
-        <v>0</v>
+        <v>2168</v>
       </c>
       <c r="BV9">
-        <v>0</v>
+        <v>276</v>
       </c>
       <c r="BW9">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="BX9">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="BY9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BZ9">
         <v>0</v>
@@ -8186,68 +8876,68 @@
       <c r="BI10">
         <v>0</v>
       </c>
-      <c r="BJ10">
-        <v>2424</v>
+      <c r="BJ10" s="10">
+        <v>19751</v>
       </c>
       <c r="BK10">
-        <v>30296</v>
+        <v>31526</v>
       </c>
       <c r="BL10">
-        <v>8176</v>
+        <v>35587</v>
       </c>
       <c r="BM10">
-        <v>277</v>
+        <v>36487</v>
       </c>
       <c r="BN10">
-        <v>1469</v>
+        <v>36241</v>
       </c>
       <c r="BO10">
-        <v>8461</v>
+        <v>35139</v>
       </c>
       <c r="BP10">
-        <v>3444</v>
+        <v>35480</v>
       </c>
       <c r="BQ10">
-        <v>1310</v>
+        <v>36103</v>
       </c>
       <c r="BR10">
-        <v>556</v>
+        <v>36020</v>
       </c>
       <c r="BS10">
-        <v>284</v>
+        <v>36145</v>
       </c>
       <c r="BT10">
-        <v>97</v>
+        <v>37294</v>
       </c>
       <c r="BU10">
-        <v>7</v>
+        <v>32129</v>
       </c>
       <c r="BV10">
+        <v>9441</v>
+      </c>
+      <c r="BW10">
+        <v>5878</v>
+      </c>
+      <c r="BX10">
+        <v>1271</v>
+      </c>
+      <c r="BY10">
+        <v>69</v>
+      </c>
+      <c r="BZ10">
+        <v>60</v>
+      </c>
+      <c r="CA10">
+        <v>11</v>
+      </c>
+      <c r="CB10">
+        <v>0</v>
+      </c>
+      <c r="CC10">
+        <v>0</v>
+      </c>
+      <c r="CD10">
         <v>1</v>
-      </c>
-      <c r="BW10">
-        <v>0</v>
-      </c>
-      <c r="BX10">
-        <v>0</v>
-      </c>
-      <c r="BY10">
-        <v>0</v>
-      </c>
-      <c r="BZ10">
-        <v>0</v>
-      </c>
-      <c r="CA10">
-        <v>0</v>
-      </c>
-      <c r="CB10">
-        <v>0</v>
-      </c>
-      <c r="CC10">
-        <v>0</v>
-      </c>
-      <c r="CD10">
-        <v>0</v>
       </c>
       <c r="CE10">
         <v>0</v>
@@ -8467,7 +9157,7 @@
       <c r="BI11">
         <v>0</v>
       </c>
-      <c r="BJ11">
+      <c r="BJ11" s="10">
         <v>0</v>
       </c>
       <c r="BK11">
@@ -8748,7 +9438,7 @@
       <c r="BI12">
         <v>0</v>
       </c>
-      <c r="BJ12">
+      <c r="BJ12" s="10">
         <v>0</v>
       </c>
       <c r="BK12">
@@ -9029,7 +9719,7 @@
       <c r="BI13">
         <v>0</v>
       </c>
-      <c r="BJ13">
+      <c r="BJ13" s="10">
         <v>0</v>
       </c>
       <c r="BK13">
@@ -9310,8 +10000,8 @@
       <c r="BI14">
         <v>0</v>
       </c>
-      <c r="BJ14">
-        <v>0</v>
+      <c r="BJ14" s="10">
+        <v>8.8538283179216595E-2</v>
       </c>
       <c r="BK14">
         <v>0</v>
@@ -9591,8 +10281,8 @@
       <c r="BI15">
         <v>0</v>
       </c>
-      <c r="BJ15">
-        <v>0</v>
+      <c r="BJ15" s="10">
+        <v>6.8701391389362806E-2</v>
       </c>
       <c r="BK15">
         <v>0</v>
@@ -9872,8 +10562,8 @@
       <c r="BI16">
         <v>0</v>
       </c>
-      <c r="BJ16">
-        <v>0</v>
+      <c r="BJ16" s="10">
+        <v>6.8928110932124101E-2</v>
       </c>
       <c r="BK16">
         <v>0</v>
@@ -10153,35 +10843,35 @@
       <c r="BI17">
         <v>0</v>
       </c>
-      <c r="BJ17">
-        <v>0</v>
+      <c r="BJ17" s="10">
+        <v>0.364117442712454</v>
       </c>
       <c r="BK17">
-        <v>0</v>
+        <v>9.6743903853192106E-2</v>
       </c>
       <c r="BL17">
-        <v>0</v>
+        <v>6.4072023708752798E-2</v>
       </c>
       <c r="BM17">
-        <v>0</v>
+        <v>8.7352524144291899E-2</v>
       </c>
       <c r="BN17">
-        <v>0</v>
+        <v>6.1868732177739701E-2</v>
       </c>
       <c r="BO17">
         <v>0</v>
       </c>
       <c r="BP17">
-        <v>0</v>
+        <v>6.2658929602465593E-2</v>
       </c>
       <c r="BQ17">
-        <v>0</v>
+        <v>8.2095883093391095E-2</v>
       </c>
       <c r="BR17">
         <v>0</v>
       </c>
       <c r="BS17">
-        <v>0</v>
+        <v>7.4323236659877306E-2</v>
       </c>
       <c r="BT17">
         <v>0</v>
@@ -10434,35 +11124,35 @@
       <c r="BI18">
         <v>0</v>
       </c>
-      <c r="BJ18">
-        <v>0</v>
+      <c r="BJ18" s="10">
+        <v>0.246683535248926</v>
       </c>
       <c r="BK18">
-        <v>0</v>
+        <v>9.4947659242208896E-2</v>
       </c>
       <c r="BL18">
-        <v>0</v>
+        <v>6.4072023708752798E-2</v>
       </c>
       <c r="BM18">
-        <v>0</v>
+        <v>7.6189954335494706E-2</v>
       </c>
       <c r="BN18">
-        <v>0</v>
+        <v>6.1868732177739701E-2</v>
       </c>
       <c r="BO18">
         <v>0</v>
       </c>
       <c r="BP18">
-        <v>0</v>
+        <v>6.2658929602465593E-2</v>
       </c>
       <c r="BQ18">
-        <v>0</v>
+        <v>8.2095883093391095E-2</v>
       </c>
       <c r="BR18">
         <v>0</v>
       </c>
       <c r="BS18">
-        <v>0</v>
+        <v>7.1002930606522394E-2</v>
       </c>
       <c r="BT18">
         <v>0</v>
@@ -10715,35 +11405,35 @@
       <c r="BI19">
         <v>0</v>
       </c>
-      <c r="BJ19">
-        <v>0</v>
+      <c r="BJ19" s="10">
+        <v>0.25086465947329001</v>
       </c>
       <c r="BK19">
-        <v>0</v>
+        <v>9.6735535499836794E-2</v>
       </c>
       <c r="BL19">
-        <v>0</v>
+        <v>6.4072023708752798E-2</v>
       </c>
       <c r="BM19">
-        <v>0</v>
+        <v>7.0647970296995904E-2</v>
       </c>
       <c r="BN19">
-        <v>0</v>
+        <v>6.1868732177739701E-2</v>
       </c>
       <c r="BO19">
         <v>0</v>
       </c>
       <c r="BP19">
-        <v>0</v>
+        <v>6.2658929602465593E-2</v>
       </c>
       <c r="BQ19">
-        <v>0</v>
+        <v>8.2095883093391095E-2</v>
       </c>
       <c r="BR19">
         <v>0</v>
       </c>
       <c r="BS19">
-        <v>0</v>
+        <v>7.1002930606522394E-2</v>
       </c>
       <c r="BT19">
         <v>0</v>
@@ -10996,50 +11686,50 @@
       <c r="BI20">
         <v>0</v>
       </c>
-      <c r="BJ20">
-        <v>4.8661422353356298E-2</v>
+      <c r="BJ20" s="10">
+        <v>1.45646977084981</v>
       </c>
       <c r="BK20">
-        <v>0.169640190738721</v>
+        <v>0.44082710028227701</v>
       </c>
       <c r="BL20">
-        <v>5.9729332378454701E-2</v>
+        <v>0.36851059944168901</v>
       </c>
       <c r="BM20">
-        <v>0</v>
+        <v>0.34941009657716698</v>
       </c>
       <c r="BN20">
-        <v>0</v>
+        <v>0.31206176068481101</v>
       </c>
       <c r="BO20">
-        <v>0</v>
+        <v>0.349995618825857</v>
       </c>
       <c r="BP20">
-        <v>4.4163694789676702E-2</v>
+        <v>0.35668714113781502</v>
       </c>
       <c r="BQ20">
-        <v>0</v>
+        <v>0.32838353237356399</v>
       </c>
       <c r="BR20">
-        <v>0</v>
+        <v>0.34055895740007402</v>
       </c>
       <c r="BS20">
-        <v>0</v>
+        <v>0.32157608354437001</v>
       </c>
       <c r="BT20">
-        <v>0</v>
+        <v>0.29500289948147401</v>
       </c>
       <c r="BU20">
-        <v>0</v>
+        <v>0.193753062125474</v>
       </c>
       <c r="BV20">
-        <v>0</v>
+        <v>9.4465161476062598E-2</v>
       </c>
       <c r="BW20">
-        <v>0</v>
+        <v>7.7414062386916102E-2</v>
       </c>
       <c r="BX20">
-        <v>0</v>
+        <v>3.5733409006959198E-2</v>
       </c>
       <c r="BY20">
         <v>0</v>
@@ -11277,50 +11967,50 @@
       <c r="BI21">
         <v>0</v>
       </c>
-      <c r="BJ21">
-        <v>3.8901972608372498E-2</v>
+      <c r="BJ21" s="10">
+        <v>0.96474323456365096</v>
       </c>
       <c r="BK21">
-        <v>0.15434875599756201</v>
+        <v>0.33901344773274</v>
       </c>
       <c r="BL21">
-        <v>5.9729332378454701E-2</v>
+        <v>0.28346670648649902</v>
       </c>
       <c r="BM21">
-        <v>0</v>
+        <v>0.24770047709967899</v>
       </c>
       <c r="BN21">
-        <v>0</v>
+        <v>0.250043088257067</v>
       </c>
       <c r="BO21">
-        <v>0</v>
+        <v>0.27235712052008199</v>
       </c>
       <c r="BP21">
-        <v>4.4163694789676702E-2</v>
+        <v>0.26837306423549701</v>
       </c>
       <c r="BQ21">
-        <v>0</v>
+        <v>0.25548604648902201</v>
       </c>
       <c r="BR21">
-        <v>0</v>
+        <v>0.26518669891186802</v>
       </c>
       <c r="BS21">
-        <v>0</v>
+        <v>0.24983874338314399</v>
       </c>
       <c r="BT21">
-        <v>0</v>
+        <v>0.22235478365160199</v>
       </c>
       <c r="BU21">
-        <v>0</v>
+        <v>0.16781073705660601</v>
       </c>
       <c r="BV21">
-        <v>0</v>
+        <v>8.7136384032104205E-2</v>
       </c>
       <c r="BW21">
-        <v>0</v>
+        <v>7.3309859099770502E-2</v>
       </c>
       <c r="BX21">
-        <v>0</v>
+        <v>3.5733409006959198E-2</v>
       </c>
       <c r="BY21">
         <v>0</v>
@@ -11558,50 +12248,50 @@
       <c r="BI22">
         <v>0</v>
       </c>
-      <c r="BJ22">
-        <v>4.0292512751549998E-2</v>
+      <c r="BJ22" s="10">
+        <v>0.98707974061158099</v>
       </c>
       <c r="BK22">
-        <v>0.15477545698098</v>
+        <v>0.33704399774803601</v>
       </c>
       <c r="BL22">
-        <v>5.9729332378454701E-2</v>
+        <v>0.27895511179972798</v>
       </c>
       <c r="BM22">
-        <v>0</v>
+        <v>0.24824285057164</v>
       </c>
       <c r="BN22">
-        <v>0</v>
+        <v>0.245734610556369</v>
       </c>
       <c r="BO22">
-        <v>0</v>
+        <v>0.264448790535254</v>
       </c>
       <c r="BP22">
-        <v>4.4163694789676702E-2</v>
+        <v>0.266820032191673</v>
       </c>
       <c r="BQ22">
-        <v>0</v>
+        <v>0.248383496757203</v>
       </c>
       <c r="BR22">
-        <v>0</v>
+        <v>0.26460625685400901</v>
       </c>
       <c r="BS22">
-        <v>0</v>
+        <v>0.24368042637594201</v>
       </c>
       <c r="BT22">
-        <v>0</v>
+        <v>0.21779301568857301</v>
       </c>
       <c r="BU22">
-        <v>0</v>
+        <v>0.16181163313008701</v>
       </c>
       <c r="BV22">
-        <v>0</v>
+        <v>8.4027856038349294E-2</v>
       </c>
       <c r="BW22">
-        <v>0</v>
+        <v>7.3309859099770502E-2</v>
       </c>
       <c r="BX22">
-        <v>0</v>
+        <v>3.5733409006959198E-2</v>
       </c>
       <c r="BY22">
         <v>0</v>
@@ -11839,53 +12529,53 @@
       <c r="BI23">
         <v>0</v>
       </c>
-      <c r="BJ23">
-        <v>0.21569684883524101</v>
+      <c r="BJ23" s="10">
+        <v>5.8258790833992702</v>
       </c>
       <c r="BK23">
-        <v>0.77298920549835903</v>
+        <v>1.76330840112911</v>
       </c>
       <c r="BL23">
-        <v>0.34353358618019803</v>
+        <v>1.4740423977667501</v>
       </c>
       <c r="BM23">
-        <v>0.11239046138888401</v>
+        <v>1.3976403863086699</v>
       </c>
       <c r="BN23">
-        <v>0.16289348377490601</v>
+        <v>1.24824704273924</v>
       </c>
       <c r="BO23">
-        <v>0.353617551303539</v>
+        <v>1.39998247530343</v>
       </c>
       <c r="BP23">
-        <v>0.25140266737031203</v>
+        <v>1.4267485645512601</v>
       </c>
       <c r="BQ23">
-        <v>0.17467080641744701</v>
+        <v>1.31353412949425</v>
       </c>
       <c r="BR23">
-        <v>0.113520007164127</v>
+        <v>1.3622358296002901</v>
       </c>
       <c r="BS23">
-        <v>9.4851262448767099E-2</v>
+        <v>1.28630433417748</v>
       </c>
       <c r="BT23">
-        <v>0</v>
+        <v>1.1800115979258901</v>
       </c>
       <c r="BU23">
-        <v>0</v>
+        <v>0.84149852023052496</v>
       </c>
       <c r="BV23">
-        <v>0</v>
+        <v>0.39422675151442699</v>
       </c>
       <c r="BW23">
-        <v>0</v>
+        <v>0.32997824592043601</v>
       </c>
       <c r="BX23">
-        <v>0</v>
+        <v>0.207023301690511</v>
       </c>
       <c r="BY23">
-        <v>0</v>
+        <v>6.4136993018082095E-2</v>
       </c>
       <c r="BZ23">
         <v>0</v>
@@ -12120,53 +12810,53 @@
       <c r="BI24">
         <v>0</v>
       </c>
-      <c r="BJ24">
-        <v>0.152014740779194</v>
+      <c r="BJ24" s="10">
+        <v>3.8589729382545999</v>
       </c>
       <c r="BK24">
-        <v>0.59065830904028005</v>
+        <v>1.3473833155107</v>
       </c>
       <c r="BL24">
-        <v>0.264615480869338</v>
+        <v>1.1016927191892001</v>
       </c>
       <c r="BM24">
-        <v>9.5808057468869806E-2</v>
+        <v>0.95567934048443903</v>
       </c>
       <c r="BN24">
-        <v>0.13887254061750701</v>
+        <v>0.98173710202131503</v>
       </c>
       <c r="BO24">
-        <v>0.27488808560690597</v>
+        <v>1.06735609732475</v>
       </c>
       <c r="BP24">
-        <v>0.192078175601887</v>
+        <v>1.0416620713254401</v>
       </c>
       <c r="BQ24">
-        <v>0.14584713646547801</v>
+        <v>0.98839277981259199</v>
       </c>
       <c r="BR24">
-        <v>9.9201860181012694E-2</v>
+        <v>1.0142042534106199</v>
       </c>
       <c r="BS24">
-        <v>9.0628065782142594E-2</v>
+        <v>0.96760124604105402</v>
       </c>
       <c r="BT24">
-        <v>0</v>
+        <v>0.87425438185005699</v>
       </c>
       <c r="BU24">
-        <v>0</v>
+        <v>0.62164457422419905</v>
       </c>
       <c r="BV24">
-        <v>0</v>
+        <v>0.29709368773612899</v>
       </c>
       <c r="BW24">
-        <v>0</v>
+        <v>0.239686683071241</v>
       </c>
       <c r="BX24">
-        <v>0</v>
+        <v>0.140098085370262</v>
       </c>
       <c r="BY24">
-        <v>0</v>
+        <v>5.8810863709424302E-2</v>
       </c>
       <c r="BZ24">
         <v>0</v>
@@ -12401,53 +13091,53 @@
       <c r="BI25">
         <v>0</v>
       </c>
-      <c r="BJ25">
-        <v>0.15032114789429099</v>
+      <c r="BJ25" s="10">
+        <v>3.94831896244632</v>
       </c>
       <c r="BK25">
-        <v>0.58248755947293596</v>
+        <v>1.32874456705976</v>
       </c>
       <c r="BL25">
-        <v>0.26004801512750098</v>
+        <v>1.0874693977698</v>
       </c>
       <c r="BM25">
-        <v>9.16635888195622E-2</v>
+        <v>0.93925395523422694</v>
       </c>
       <c r="BN25">
-        <v>0.136267556673488</v>
+        <v>0.97304386268497201</v>
       </c>
       <c r="BO25">
-        <v>0.267185440969606</v>
+        <v>1.0474471126536</v>
       </c>
       <c r="BP25">
-        <v>0.19109871725774799</v>
+        <v>1.05130329716535</v>
       </c>
       <c r="BQ25">
-        <v>0.14665584107700899</v>
+        <v>0.97549465813718705</v>
       </c>
       <c r="BR25">
-        <v>9.8035599381146699E-2</v>
+        <v>1.01255261717211</v>
       </c>
       <c r="BS25">
-        <v>9.0656416954964805E-2</v>
+        <v>0.95694137652901201</v>
       </c>
       <c r="BT25">
-        <v>0</v>
+        <v>0.86662921931234904</v>
       </c>
       <c r="BU25">
-        <v>0</v>
+        <v>0.61957732545278199</v>
       </c>
       <c r="BV25">
-        <v>0</v>
+        <v>0.29011208709935798</v>
       </c>
       <c r="BW25">
-        <v>0</v>
+        <v>0.22943476824447401</v>
       </c>
       <c r="BX25">
-        <v>0</v>
+        <v>0.13815182571484799</v>
       </c>
       <c r="BY25">
-        <v>0</v>
+        <v>5.8810863709424302E-2</v>
       </c>
       <c r="BZ25">
         <v>0</v>
@@ -12682,59 +13372,59 @@
       <c r="BI26">
         <v>0</v>
       </c>
-      <c r="BJ26">
-        <v>0.86278739534096405</v>
+      <c r="BJ26" s="10">
+        <v>23.303516333596999</v>
       </c>
       <c r="BK26">
-        <v>3.0919568219934299</v>
+        <v>7.0532336045164401</v>
       </c>
       <c r="BL26">
-        <v>1.3741343447207901</v>
+        <v>5.8961695910670304</v>
       </c>
       <c r="BM26">
-        <v>0.44956184555553802</v>
+        <v>5.5905615452346797</v>
       </c>
       <c r="BN26">
-        <v>0.67522408509649601</v>
+        <v>4.9929881709569903</v>
       </c>
       <c r="BO26">
-        <v>1.41447020521415</v>
+        <v>5.59992990121372</v>
       </c>
       <c r="BP26">
-        <v>1.0056106694812501</v>
+        <v>5.7069942582050501</v>
       </c>
       <c r="BQ26">
-        <v>0.69868322566978902</v>
+        <v>5.2541365179770301</v>
       </c>
       <c r="BR26">
-        <v>0.49997422703559102</v>
+        <v>5.4489433184011897</v>
       </c>
       <c r="BS26">
-        <v>0.41039517207946702</v>
+        <v>5.1452173367099201</v>
       </c>
       <c r="BT26">
-        <v>0.29087978953708399</v>
+        <v>4.7200463917035904</v>
       </c>
       <c r="BU26">
-        <v>0.109001925687746</v>
+        <v>3.3659940809220998</v>
       </c>
       <c r="BV26">
-        <v>4.7176937956212202E-2</v>
+        <v>1.5769070060577</v>
       </c>
       <c r="BW26">
-        <v>0</v>
+        <v>1.31991298368174</v>
       </c>
       <c r="BX26">
-        <v>0</v>
+        <v>0.82809320676204701</v>
       </c>
       <c r="BY26">
-        <v>0</v>
+        <v>0.25654797207232799</v>
       </c>
       <c r="BZ26">
-        <v>0</v>
+        <v>0.222251482545891</v>
       </c>
       <c r="CA26">
-        <v>0</v>
+        <v>9.9435289991700204E-2</v>
       </c>
       <c r="CB26">
         <v>0</v>
@@ -12743,7 +13433,7 @@
         <v>0</v>
       </c>
       <c r="CD26">
-        <v>0</v>
+        <v>3.8007533029403198E-2</v>
       </c>
       <c r="CE26">
         <v>0</v>
@@ -12963,59 +13653,59 @@
       <c r="BI27">
         <v>0</v>
       </c>
-      <c r="BJ27">
-        <v>0.57149713587328199</v>
+      <c r="BJ27" s="10">
+        <v>15.435891753018399</v>
       </c>
       <c r="BK27">
-        <v>2.3626332361611202</v>
+        <v>5.3895332620428302</v>
       </c>
       <c r="BL27">
-        <v>1.02702188556862</v>
+        <v>4.4067708767568003</v>
       </c>
       <c r="BM27">
-        <v>0.31140321678378102</v>
+        <v>3.8227173619377499</v>
       </c>
       <c r="BN27">
-        <v>0.53105876787537998</v>
+        <v>3.9269484080852601</v>
       </c>
       <c r="BO27">
-        <v>1.07840164047541</v>
+        <v>4.269424389299</v>
       </c>
       <c r="BP27">
-        <v>0.73419137677286495</v>
+        <v>4.1666482853017603</v>
       </c>
       <c r="BQ27">
-        <v>0.52573697180987999</v>
+        <v>3.9535711192503702</v>
       </c>
       <c r="BR27">
-        <v>0.37223803443695602</v>
+        <v>4.0568170136424797</v>
       </c>
       <c r="BS27">
-        <v>0.31068800013665299</v>
+        <v>3.8704049841642099</v>
       </c>
       <c r="BT27">
-        <v>0.21924704056951999</v>
+        <v>3.4970175274002302</v>
       </c>
       <c r="BU27">
-        <v>0.102183321984385</v>
+        <v>2.48657829689679</v>
       </c>
       <c r="BV27">
-        <v>4.7176937956212202E-2</v>
+        <v>1.1593826642456899</v>
       </c>
       <c r="BW27">
-        <v>0</v>
+        <v>0.93037993399946095</v>
       </c>
       <c r="BX27">
-        <v>0</v>
+        <v>0.51295163324590598</v>
       </c>
       <c r="BY27">
-        <v>0</v>
+        <v>0.18669543516553999</v>
       </c>
       <c r="BZ27">
-        <v>0</v>
+        <v>0.14209902522738199</v>
       </c>
       <c r="CA27">
-        <v>0</v>
+        <v>8.3269755819208702E-2</v>
       </c>
       <c r="CB27">
         <v>0</v>
@@ -13024,7 +13714,7 @@
         <v>0</v>
       </c>
       <c r="CD27">
-        <v>0</v>
+        <v>3.8007533029403198E-2</v>
       </c>
       <c r="CE27">
         <v>0</v>
@@ -13244,59 +13934,59 @@
       <c r="BI28">
         <v>0</v>
       </c>
-      <c r="BJ28">
-        <v>0.58472889410829598</v>
+      <c r="BJ28" s="10">
+        <v>15.793275849785299</v>
       </c>
       <c r="BK28">
-        <v>2.3299502378917398</v>
+        <v>5.31497826823907</v>
       </c>
       <c r="BL28">
-        <v>1.0137625963688299</v>
+        <v>4.3498775910792</v>
       </c>
       <c r="BM28">
-        <v>0.306071282366502</v>
+        <v>3.7570158209368998</v>
       </c>
       <c r="BN28">
-        <v>0.52635626558558801</v>
+        <v>3.8921754507398898</v>
       </c>
       <c r="BO28">
-        <v>1.05828662750417</v>
+        <v>4.1897884506144303</v>
       </c>
       <c r="BP28">
-        <v>0.74098677143098601</v>
+        <v>4.2052131886613999</v>
       </c>
       <c r="BQ28">
-        <v>0.51887631927252698</v>
+        <v>3.9019786325487398</v>
       </c>
       <c r="BR28">
-        <v>0.37163184310577502</v>
+        <v>4.0502104686884399</v>
       </c>
       <c r="BS28">
-        <v>0.30634777641139499</v>
+        <v>3.8277655061160498</v>
       </c>
       <c r="BT28">
-        <v>0.21474903018844099</v>
+        <v>3.4665168772493899</v>
       </c>
       <c r="BU28">
-        <v>0.102479103029744</v>
+        <v>2.47830930181112</v>
       </c>
       <c r="BV28">
-        <v>4.7176937956212202E-2</v>
+        <v>1.1419710987338401</v>
       </c>
       <c r="BW28">
-        <v>0</v>
+        <v>0.91202168021336305</v>
       </c>
       <c r="BX28">
-        <v>0</v>
+        <v>0.48726132975127301</v>
       </c>
       <c r="BY28">
-        <v>0</v>
+        <v>0.18676423010967599</v>
       </c>
       <c r="BZ28">
-        <v>0</v>
+        <v>0.13490568895159799</v>
       </c>
       <c r="CA28">
-        <v>0</v>
+        <v>8.3938640968767797E-2</v>
       </c>
       <c r="CB28">
         <v>0</v>
@@ -13305,7 +13995,7 @@
         <v>0</v>
       </c>
       <c r="CD28">
-        <v>0</v>
+        <v>3.8007533029403198E-2</v>
       </c>
       <c r="CE28">
         <v>0</v>
@@ -13525,7 +14215,7 @@
       <c r="BI29">
         <v>1.3141996124999999</v>
       </c>
-      <c r="BJ29">
+      <c r="BJ29" s="10">
         <v>12.6789259225</v>
       </c>
       <c r="BK29">
@@ -13626,281 +14316,281 @@
       <c r="A30" t="s">
         <v>33</v>
       </c>
-      <c r="B30" s="2">
-        <v>2.2880339138783499E-6</v>
-      </c>
-      <c r="C30" s="2">
-        <v>2.3166658998962598E-6</v>
-      </c>
-      <c r="D30" s="2">
-        <v>2.4974510258016099E-6</v>
-      </c>
-      <c r="E30" s="2">
-        <v>2.3362098770244698E-6</v>
-      </c>
-      <c r="F30" s="2">
-        <v>1.51333953548655E-6</v>
-      </c>
-      <c r="G30" s="2">
-        <v>1.6442568051698E-6</v>
-      </c>
-      <c r="H30" s="2">
-        <v>2.3394982528216099E-6</v>
-      </c>
-      <c r="I30" s="2">
-        <v>2.2679735908638599E-6</v>
-      </c>
-      <c r="J30" s="2">
-        <v>2.1253429740066598E-6</v>
-      </c>
-      <c r="K30" s="2">
-        <v>1.77782321947317E-6</v>
-      </c>
-      <c r="L30" s="2">
-        <v>2.03431169361831E-6</v>
-      </c>
-      <c r="M30" s="2">
-        <v>2.3424613742538201E-6</v>
-      </c>
-      <c r="N30" s="2">
-        <v>2.06512615342148E-6</v>
-      </c>
-      <c r="O30" s="2">
-        <v>2.1573598304823502E-6</v>
-      </c>
-      <c r="P30" s="2">
-        <v>1.33989054137762E-6</v>
-      </c>
-      <c r="Q30" s="2">
-        <v>1.5290213907509701E-6</v>
-      </c>
-      <c r="R30" s="2">
-        <v>1.94341259619611E-6</v>
-      </c>
-      <c r="S30" s="2">
-        <v>1.9407647415474302E-6</v>
-      </c>
-      <c r="T30" s="2">
-        <v>2.0350656086627198E-6</v>
-      </c>
-      <c r="U30" s="2">
-        <v>1.9183897587438199E-6</v>
-      </c>
-      <c r="V30" s="2">
-        <v>1.7900432375371199E-6</v>
-      </c>
-      <c r="W30" s="2">
-        <v>2.4502923017615601E-6</v>
-      </c>
-      <c r="X30" s="2">
-        <v>3.25725725571424E-6</v>
-      </c>
-      <c r="Y30" s="2">
-        <v>2.4268052233842101E-6</v>
-      </c>
-      <c r="Z30" s="2">
-        <v>2.1275506513089701E-6</v>
-      </c>
-      <c r="AA30" s="2">
-        <v>1.5547456400179199E-6</v>
-      </c>
-      <c r="AB30" s="2">
-        <v>1.3707113453107E-6</v>
-      </c>
-      <c r="AC30" s="2">
-        <v>1.38728352233035E-6</v>
-      </c>
-      <c r="AD30" s="2">
-        <v>1.4750845909102401E-6</v>
-      </c>
-      <c r="AE30" s="2">
-        <v>1.5616971506375101E-6</v>
-      </c>
-      <c r="AF30" s="2">
-        <v>1.2843962919338499E-6</v>
-      </c>
-      <c r="AG30" s="2">
-        <v>1.34739849351715E-6</v>
-      </c>
-      <c r="AH30" s="2">
-        <v>1.96145169357832E-6</v>
-      </c>
-      <c r="AI30" s="2">
-        <v>2.21230109360631E-6</v>
-      </c>
-      <c r="AJ30" s="2">
-        <v>1.7415072660345899E-6</v>
-      </c>
-      <c r="AK30" s="2">
-        <v>1.7415072660345899E-6</v>
-      </c>
-      <c r="AL30" s="2">
-        <v>2.38515180286167E-6</v>
-      </c>
-      <c r="AM30" s="2">
-        <v>1.9167744779342999E-6</v>
-      </c>
-      <c r="AN30" s="2">
-        <v>1.1413734455688901E-6</v>
-      </c>
-      <c r="AO30" s="2">
-        <v>1.21249339865022E-6</v>
-      </c>
-      <c r="AP30" s="2">
-        <v>1.9325328565379001E-6</v>
-      </c>
-      <c r="AQ30" s="2">
-        <v>1.75620123871448E-6</v>
-      </c>
-      <c r="AR30" s="2">
-        <v>1.62236269293128E-6</v>
-      </c>
-      <c r="AS30" s="2">
-        <v>1.81238349792874E-6</v>
-      </c>
-      <c r="AT30" s="2">
-        <v>1.2553732186330101E-6</v>
-      </c>
-      <c r="AU30" s="2">
-        <v>1.1719268588960001E-6</v>
-      </c>
-      <c r="AV30" s="2">
-        <v>1.4855491306764301E-6</v>
-      </c>
-      <c r="AW30" s="2">
-        <v>1.86202170728117E-6</v>
-      </c>
-      <c r="AX30" s="2">
-        <v>2.01296537982452E-6</v>
-      </c>
-      <c r="AY30" s="2">
-        <v>2.2893484400696301E-6</v>
-      </c>
-      <c r="AZ30" s="2">
-        <v>2.0239442814575399E-6</v>
-      </c>
-      <c r="BA30" s="2">
-        <v>1.7040172007631401E-6</v>
-      </c>
-      <c r="BB30" s="2">
-        <v>1.82044272754136E-6</v>
-      </c>
-      <c r="BC30" s="2">
-        <v>1.35183913922563E-6</v>
-      </c>
-      <c r="BD30" s="2">
-        <v>9.2103815913760504E-7</v>
-      </c>
-      <c r="BE30" s="2">
-        <v>9.8404403032751892E-7</v>
-      </c>
-      <c r="BF30" s="2">
-        <v>1.22627175394725E-6</v>
-      </c>
-      <c r="BG30" s="2">
-        <v>1.28113791916581E-6</v>
-      </c>
-      <c r="BH30" s="2">
-        <v>1.50963485366586E-6</v>
-      </c>
-      <c r="BI30" s="2">
-        <v>2.2474957371565198E-5</v>
-      </c>
-      <c r="BJ30">
-        <v>0.35849904698993101</v>
+      <c r="B30">
+        <v>3.4552855299263102E-4</v>
+      </c>
+      <c r="C30">
+        <v>3.4922695701364699E-4</v>
+      </c>
+      <c r="D30">
+        <v>3.7243094791539801E-4</v>
+      </c>
+      <c r="E30">
+        <v>3.5174768035326398E-4</v>
+      </c>
+      <c r="F30">
+        <v>2.4254340313737601E-4</v>
+      </c>
+      <c r="G30">
+        <v>2.6039820755555099E-4</v>
+      </c>
+      <c r="H30">
+        <v>3.5217150633777398E-4</v>
+      </c>
+      <c r="I30">
+        <v>3.42933388528255E-4</v>
+      </c>
+      <c r="J30">
+        <v>3.2438422540832302E-4</v>
+      </c>
+      <c r="K30">
+        <v>2.7840459463249602E-4</v>
+      </c>
+      <c r="L30">
+        <v>3.1245229905066602E-4</v>
+      </c>
+      <c r="M30">
+        <v>3.52553338134593E-4</v>
+      </c>
+      <c r="N30">
+        <v>3.1649974143492201E-4</v>
+      </c>
+      <c r="O30">
+        <v>3.2856322036848001E-4</v>
+      </c>
+      <c r="P30">
+        <v>2.1853919167599001E-4</v>
+      </c>
+      <c r="Q30">
+        <v>2.4469350293576301E-4</v>
+      </c>
+      <c r="R30">
+        <v>3.00460766955036E-4</v>
+      </c>
+      <c r="S30">
+        <v>3.00110265199284E-4</v>
+      </c>
+      <c r="T30">
+        <v>3.1255142965845302E-4</v>
+      </c>
+      <c r="U30">
+        <v>2.9714568613054302E-4</v>
+      </c>
+      <c r="V30">
+        <v>2.8004207508428399E-4</v>
+      </c>
+      <c r="W30">
+        <v>3.6640208500066497E-4</v>
+      </c>
+      <c r="X30">
+        <v>4.6752265259819901E-4</v>
+      </c>
+      <c r="Y30">
+        <v>3.6339323708336498E-4</v>
+      </c>
+      <c r="Z30">
+        <v>3.2467267143425902E-4</v>
+      </c>
+      <c r="AA30">
+        <v>2.4821364068843699E-4</v>
+      </c>
+      <c r="AB30">
+        <v>2.22835758939084E-4</v>
+      </c>
+      <c r="AC30">
+        <v>2.2514023902480399E-4</v>
+      </c>
+      <c r="AD30">
+        <v>2.37284826806665E-4</v>
+      </c>
+      <c r="AE30">
+        <v>2.4916345062835299E-4</v>
+      </c>
+      <c r="AF30">
+        <v>2.1076685359518299E-4</v>
+      </c>
+      <c r="AG30">
+        <v>2.1958713422653899E-4</v>
+      </c>
+      <c r="AH30">
+        <v>3.0284681494558498E-4</v>
+      </c>
+      <c r="AI30">
+        <v>3.3571372849145798E-4</v>
+      </c>
+      <c r="AJ30">
+        <v>2.7352864986342402E-4</v>
+      </c>
+      <c r="AK30">
+        <v>2.7352864986342402E-4</v>
+      </c>
+      <c r="AL30">
+        <v>3.5804682058401799E-4</v>
+      </c>
+      <c r="AM30">
+        <v>2.9693147716718598E-4</v>
+      </c>
+      <c r="AN30">
+        <v>1.9050586157562399E-4</v>
+      </c>
+      <c r="AO30">
+        <v>2.0062390286668699E-4</v>
+      </c>
+      <c r="AP30">
+        <v>2.9902015430051398E-4</v>
+      </c>
+      <c r="AQ30">
+        <v>2.7550327473734298E-4</v>
+      </c>
+      <c r="AR30">
+        <v>2.5742692223349102E-4</v>
+      </c>
+      <c r="AS30">
+        <v>2.8303151913530201E-4</v>
+      </c>
+      <c r="AT30">
+        <v>2.0668282307117599E-4</v>
+      </c>
+      <c r="AU30">
+        <v>1.9486341033488801E-4</v>
+      </c>
+      <c r="AV30">
+        <v>2.38725225658476E-4</v>
+      </c>
+      <c r="AW30">
+        <v>2.8965496137920002E-4</v>
+      </c>
+      <c r="AX30">
+        <v>3.0964331756237398E-4</v>
+      </c>
+      <c r="AY30">
+        <v>3.4569849607390702E-4</v>
+      </c>
+      <c r="AZ30">
+        <v>3.1108857401131602E-4</v>
+      </c>
+      <c r="BA30">
+        <v>2.6847968775958102E-4</v>
+      </c>
+      <c r="BB30">
+        <v>2.8410865432669502E-4</v>
+      </c>
+      <c r="BC30">
+        <v>2.20206553634978E-4</v>
+      </c>
+      <c r="BD30">
+        <v>1.5854821863972999E-4</v>
+      </c>
+      <c r="BE30">
+        <v>1.6778896115252699E-4</v>
+      </c>
+      <c r="BF30">
+        <v>2.02574096387212E-4</v>
+      </c>
+      <c r="BG30">
+        <v>2.1030901323051799E-4</v>
+      </c>
+      <c r="BH30">
+        <v>2.4203499643925101E-4</v>
+      </c>
+      <c r="BI30">
+        <v>2.44314750412608E-3</v>
+      </c>
+      <c r="BJ30" s="10">
+        <v>9.6829050148094105</v>
       </c>
       <c r="BK30">
-        <v>4.2447373637128996</v>
+        <v>9.6829050148094105</v>
       </c>
       <c r="BL30">
-        <v>2.25665360059635</v>
+        <v>9.6829050148094105</v>
       </c>
       <c r="BM30">
-        <v>0.77864533169816397</v>
+        <v>9.6829050148094105</v>
       </c>
       <c r="BN30">
-        <v>1.30946248135273</v>
+        <v>9.6829050148094105</v>
       </c>
       <c r="BO30">
-        <v>2.4457771587955301</v>
+        <v>9.6829050148094105</v>
       </c>
       <c r="BP30">
-        <v>1.7061928142740399</v>
+        <v>9.6829050148094105</v>
       </c>
       <c r="BQ30">
-        <v>1.2876108731227101</v>
+        <v>9.6829050148094105</v>
       </c>
       <c r="BR30">
-        <v>0.88846638096727104</v>
+        <v>9.6829050148094105</v>
       </c>
       <c r="BS30">
-        <v>0.77233228640824803</v>
+        <v>9.6829050148094105</v>
       </c>
       <c r="BT30">
-        <v>0.59672323935688598</v>
+        <v>9.6829050148094105</v>
       </c>
       <c r="BU30">
-        <v>0.25044793281140099</v>
+        <v>7.12281785194559</v>
       </c>
       <c r="BV30">
-        <v>0.109450654368778</v>
+        <v>3.5065518659825199</v>
       </c>
       <c r="BW30">
-        <v>9.1255374022131297E-2</v>
+        <v>3.0011086513471801</v>
       </c>
       <c r="BX30">
-        <v>4.4908794177954202E-2</v>
+        <v>1.6355416071517801</v>
       </c>
       <c r="BY30">
-        <v>1.2469783504636201E-2</v>
+        <v>0.54608304553468101</v>
       </c>
       <c r="BZ30">
-        <v>7.6947549928068496E-3</v>
+        <v>0.36121242032510598</v>
       </c>
       <c r="CA30">
-        <v>4.1258435799812797E-3</v>
+        <v>0.211850000352764</v>
       </c>
       <c r="CB30">
-        <v>1.5911823745653399E-3</v>
+        <v>9.3707723485290606E-2</v>
       </c>
       <c r="CC30">
-        <v>1.37423937768449E-3</v>
+        <v>8.2656566622323499E-2</v>
       </c>
       <c r="CD30">
-        <v>1.3947651725774799E-3</v>
+        <v>8.3712365942361103E-2</v>
       </c>
       <c r="CE30">
-        <v>9.8845877283098909E-4</v>
+        <v>6.2339658955267198E-2</v>
       </c>
       <c r="CF30">
-        <v>6.2726689798427301E-4</v>
+        <v>4.2235433309792299E-2</v>
       </c>
       <c r="CG30">
-        <v>4.4970477699700899E-4</v>
+        <v>3.1764896496682397E-2</v>
       </c>
       <c r="CH30">
-        <v>4.4490684436301301E-4</v>
+        <v>3.14745347596493E-2</v>
       </c>
       <c r="CI30">
-        <v>2.8805372821976203E-4</v>
+        <v>2.1693474037470101E-2</v>
       </c>
       <c r="CJ30">
-        <v>3.3982292313158098E-4</v>
+        <v>2.4990798526656501E-2</v>
       </c>
       <c r="CK30">
-        <v>3.5298444055644899E-4</v>
+        <v>2.5817159641297601E-2</v>
       </c>
       <c r="CL30">
-        <v>2.2257598703003499E-4</v>
+        <v>1.7395970030996001E-2</v>
       </c>
       <c r="CM30">
-        <v>1.86172225613053E-4</v>
+        <v>1.49295136285098E-2</v>
       </c>
       <c r="CN30">
-        <v>2.1225419931479299E-4</v>
+        <v>1.6702977258617299E-2</v>
       </c>
       <c r="CO30">
-        <v>2.0512672887656701E-4</v>
+        <v>1.62216224539538E-2</v>
       </c>
     </row>
     <row r="31" spans="1:97" x14ac:dyDescent="0.25">
@@ -14087,7 +14777,7 @@
       <c r="BI31" s="1">
         <v>44776.615277777775</v>
       </c>
-      <c r="BJ31" s="1">
+      <c r="BJ31" s="11">
         <v>44776.625694444447</v>
       </c>
       <c r="BK31" s="1">
@@ -14189,7 +14879,7 @@
       <c r="CS31" s="1"/>
     </row>
     <row r="32" spans="1:97" x14ac:dyDescent="0.25">
-      <c r="BK32" t="s">
+      <c r="BJ32" s="10" t="s">
         <v>46</v>
       </c>
     </row>
@@ -14208,6 +14898,9 @@
       </c>
       <c r="H33" t="s">
         <v>31</v>
+      </c>
+      <c r="I33" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.25">
@@ -14217,23 +14910,26 @@
       </c>
       <c r="B34" s="9">
         <f>MAX(B2:CS2)</f>
-        <v>3.0194890839779602E-3</v>
+        <v>2.2757340169528399E-2</v>
       </c>
       <c r="C34" s="6">
         <f>_xlfn.XLOOKUP(MAX(B2:CS2), B2:CS2, $B$1:$CS$1)</f>
-        <v>44776.636111111111</v>
+        <v>44776.625694444447</v>
       </c>
       <c r="E34" s="1">
         <v>44776.000694444447</v>
       </c>
       <c r="F34" s="2">
-        <v>9.4170832457325001E-10</v>
+        <v>1.4221254009907999E-7</v>
       </c>
       <c r="G34" s="2">
-        <v>6.7817983640293597E-10</v>
+        <v>1.0241565744345101E-7</v>
       </c>
       <c r="H34" s="2">
-        <v>6.6705963235866703E-10</v>
+        <v>1.0073633442779E-7</v>
+      </c>
+      <c r="I34">
+        <v>0.76957219099999996</v>
       </c>
       <c r="V34" t="s">
         <v>45</v>
@@ -14246,23 +14942,26 @@
       </c>
       <c r="B35" s="9">
         <f t="shared" ref="B35:B60" si="1">MAX(B3:CS3)</f>
-        <v>2.30725901968859E-3</v>
+        <v>1.5074113040056999E-2</v>
       </c>
       <c r="C35" s="6">
         <f t="shared" ref="C35:C59" si="2">_xlfn.XLOOKUP(MAX(B3:CS3), B3:CS3, $B$1:$CS$1)</f>
-        <v>44776.636111111111</v>
+        <v>44776.625694444447</v>
       </c>
       <c r="E35" s="1">
         <v>44776.011111111111</v>
       </c>
       <c r="F35" s="2">
-        <v>1.19225420553501E-9</v>
+        <v>1.79726955104284E-7</v>
       </c>
       <c r="G35" s="2">
-        <v>7.9935488811814302E-10</v>
+        <v>1.20499151459588E-7</v>
       </c>
       <c r="H35" s="2">
-        <v>7.8287815236245401E-10</v>
+        <v>1.18015357706683E-7</v>
+      </c>
+      <c r="I35">
+        <v>0.771817164</v>
       </c>
       <c r="T35" t="s">
         <v>0</v>
@@ -14281,23 +14980,26 @@
       </c>
       <c r="B36" s="9">
         <f t="shared" si="1"/>
-        <v>2.27534202919115E-3</v>
+        <v>1.5423120947055899E-2</v>
       </c>
       <c r="C36" s="6">
         <f t="shared" si="2"/>
-        <v>44776.636111111111</v>
+        <v>44776.625694444447</v>
       </c>
       <c r="E36" s="1">
         <v>44776.021527777775</v>
       </c>
       <c r="F36" s="2">
-        <v>1.13718472474984E-9</v>
+        <v>1.69582018075944E-7</v>
       </c>
       <c r="G36" s="2">
-        <v>8.0473361940703399E-10</v>
+        <v>1.20005438184596E-7</v>
       </c>
       <c r="H36" s="2">
-        <v>7.8143387235638396E-10</v>
+        <v>1.16530876805227E-7</v>
+      </c>
+      <c r="I36">
+        <v>0.78552173950000004</v>
       </c>
       <c r="T36" t="s">
         <v>1</v>
@@ -14326,13 +15028,16 @@
         <v>44776.031944444447</v>
       </c>
       <c r="F37" s="2">
-        <v>1.0151142238303101E-9</v>
+        <v>1.52839039433596E-7</v>
       </c>
       <c r="G37" s="2">
-        <v>7.2252814219493303E-10</v>
+        <v>1.08786286926953E-7</v>
       </c>
       <c r="H37" s="2">
-        <v>7.0875576954331898E-10</v>
+        <v>1.0671267180346699E-7</v>
+      </c>
+      <c r="I37">
+        <v>0.77333739349999997</v>
       </c>
       <c r="T37" t="s">
         <v>2</v>
@@ -14351,23 +15056,26 @@
       </c>
       <c r="B38">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="C38" s="3">
         <f t="shared" si="2"/>
-        <v>44776.000694444447</v>
+        <v>44776.625694444447</v>
       </c>
       <c r="E38" s="1">
         <v>44776.042361111111</v>
       </c>
       <c r="F38" s="2">
-        <v>6.4398678510234201E-10</v>
+        <v>1.0321196451396E-7</v>
       </c>
       <c r="G38" s="2">
-        <v>4.4567946577085499E-10</v>
+        <v>7.1429188097304793E-8</v>
       </c>
       <c r="H38" s="2">
-        <v>4.2747369092617503E-10</v>
+        <v>6.8511342838640803E-8</v>
+      </c>
+      <c r="I38">
+        <v>0.69855224699999996</v>
       </c>
       <c r="T38" t="s">
         <v>3</v>
@@ -14386,23 +15094,26 @@
       </c>
       <c r="B39">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>474</v>
       </c>
       <c r="C39" s="3">
         <f t="shared" si="2"/>
-        <v>44776.000694444447</v>
+        <v>44776.625694444447</v>
       </c>
       <c r="E39" s="1">
         <v>44776.052777777775</v>
       </c>
       <c r="F39" s="2">
-        <v>6.2715093817983104E-10</v>
+        <v>9.9320847969424001E-8</v>
       </c>
       <c r="G39" s="2">
-        <v>4.6111146412390699E-10</v>
+        <v>7.30254534228644E-8</v>
       </c>
       <c r="H39" s="2">
-        <v>4.45093909203132E-10</v>
+        <v>7.0488779968203097E-8</v>
+      </c>
+      <c r="I39">
+        <v>0.71226070049999901</v>
       </c>
       <c r="T39" t="s">
         <v>4</v>
@@ -14421,23 +15132,26 @@
       </c>
       <c r="B40" s="5">
         <f>MAX(B8:CO8)</f>
-        <v>26</v>
+        <v>5962</v>
       </c>
       <c r="C40" s="6">
         <f t="shared" si="2"/>
-        <v>44776.636111111111</v>
+        <v>44776.625694444447</v>
       </c>
       <c r="E40" s="1">
         <v>44776.063194444447</v>
       </c>
       <c r="F40" s="2">
-        <v>9.9990196305767197E-10</v>
+        <v>1.5051816349752101E-7</v>
       </c>
       <c r="G40" s="2">
-        <v>6.9556006144983501E-10</v>
+        <v>1.04704687978662E-7</v>
       </c>
       <c r="H40" s="2">
-        <v>6.6392990013645499E-10</v>
+        <v>9.9943307395675201E-8</v>
+      </c>
+      <c r="I40">
+        <v>0.773592222</v>
       </c>
       <c r="T40" t="s">
         <v>5</v>
@@ -14456,23 +15170,26 @@
       </c>
       <c r="B41" s="5">
         <f t="shared" ref="B41:B42" si="3">MAX(B9:CO9)</f>
-        <v>1832</v>
+        <v>27015</v>
       </c>
       <c r="C41" s="6">
         <f t="shared" si="2"/>
-        <v>44776.636111111111</v>
+        <v>44776.625694444447</v>
       </c>
       <c r="E41" s="1">
         <v>44776.073611111111</v>
       </c>
       <c r="F41" s="2">
-        <v>1.02326911631512E-9</v>
+        <v>1.54725410758714E-7</v>
       </c>
       <c r="G41" s="2">
-        <v>6.7940669377925398E-10</v>
+        <v>1.02731019720165E-7</v>
       </c>
       <c r="H41" s="2">
-        <v>6.5978128215744202E-10</v>
+        <v>9.9763520923234002E-8</v>
+      </c>
+      <c r="I41">
+        <v>0.76798645399999999</v>
       </c>
       <c r="T41" t="s">
         <v>6</v>
@@ -14491,23 +15208,26 @@
       </c>
       <c r="B42" s="5">
         <f t="shared" si="3"/>
-        <v>30296</v>
+        <v>37294</v>
       </c>
       <c r="C42" s="6">
         <f t="shared" si="2"/>
-        <v>44776.636111111111</v>
+        <v>44776.729861111111</v>
       </c>
       <c r="E42" s="1">
         <v>44776.084027777775</v>
       </c>
       <c r="F42" s="2">
-        <v>9.5971722737034707E-10</v>
+        <v>1.4647853697863599E-7</v>
       </c>
       <c r="G42" s="2">
-        <v>6.4767005517130501E-10</v>
+        <v>9.8851786152673197E-8</v>
       </c>
       <c r="H42" s="2">
-        <v>6.2250654971797597E-10</v>
+        <v>9.5011161685906004E-8</v>
+      </c>
+      <c r="I42">
+        <v>0.7563906655</v>
       </c>
       <c r="T42" t="s">
         <v>7</v>
@@ -14536,13 +15256,16 @@
         <v>44776.094444444447</v>
       </c>
       <c r="F43" s="2">
-        <v>7.9877157460493596E-10</v>
+        <v>1.250864956627E-7</v>
       </c>
       <c r="G43" s="2">
-        <v>5.4184663617276897E-10</v>
+        <v>8.4852414708764497E-8</v>
       </c>
       <c r="H43" s="2">
-        <v>5.3286742621083799E-10</v>
+        <v>8.3446283164622004E-8</v>
+      </c>
+      <c r="I43">
+        <v>0.72541048299999999</v>
       </c>
       <c r="T43" t="s">
         <v>8</v>
@@ -14571,13 +15294,16 @@
         <v>44776.104861111111</v>
       </c>
       <c r="F44" s="2">
-        <v>9.7700202241142105E-10</v>
+        <v>1.5005887693287601E-7</v>
       </c>
       <c r="G44" s="2">
-        <v>6.2835086765185102E-10</v>
+        <v>9.6509140572479604E-8</v>
       </c>
       <c r="H44" s="2">
-        <v>6.0535869958787201E-10</v>
+        <v>9.29777467387017E-8</v>
+      </c>
+      <c r="I44">
+        <v>0.74867457049999997</v>
       </c>
     </row>
     <row r="45" spans="1:27" x14ac:dyDescent="0.25">
@@ -14597,13 +15323,16 @@
         <v>44776.115277777775</v>
       </c>
       <c r="F45" s="2">
-        <v>9.4746727011196394E-10</v>
+        <v>1.4259904240921899E-7</v>
       </c>
       <c r="G45" s="2">
-        <v>7.4436162291078E-10</v>
+        <v>1.1203052388438301E-7</v>
       </c>
       <c r="H45" s="2">
-        <v>7.3707415853799905E-10</v>
+        <v>1.10933720359415E-7</v>
+      </c>
+      <c r="I45">
+        <v>0.77382161049999998</v>
       </c>
       <c r="U45" t="s">
         <v>37</v>
@@ -14616,23 +15345,26 @@
       </c>
       <c r="B46">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>8.8538283179216595E-2</v>
       </c>
       <c r="C46" s="3">
         <f t="shared" si="2"/>
-        <v>44776.000694444447</v>
+        <v>44776.625694444447</v>
       </c>
       <c r="E46" s="1">
         <v>44776.125694444447</v>
       </c>
       <c r="F46" s="2">
-        <v>9.9179274251827295E-10</v>
+        <v>1.52001438766829E-7</v>
       </c>
       <c r="G46" s="2">
-        <v>6.45184550477534E-10</v>
+        <v>9.8880517814838898E-8</v>
       </c>
       <c r="H46" s="2">
-        <v>6.3212548690507896E-10</v>
+        <v>9.6879095171269695E-8</v>
+      </c>
+      <c r="I46">
+        <v>0.75131557849999997</v>
       </c>
       <c r="U46" t="s">
         <v>35</v>
@@ -14660,23 +15392,26 @@
       </c>
       <c r="B47">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>6.8701391389362806E-2</v>
       </c>
       <c r="C47" s="3">
         <f t="shared" si="2"/>
-        <v>44776.000694444447</v>
+        <v>44776.625694444447</v>
       </c>
       <c r="E47" s="1">
         <v>44776.136111111111</v>
       </c>
       <c r="F47" s="2">
-        <v>9.0412029372403197E-10</v>
+        <v>1.3769639682143201E-7</v>
       </c>
       <c r="G47" s="2">
-        <v>6.5859411579469405E-10</v>
+        <v>1.00303065136692E-7</v>
       </c>
       <c r="H47" s="2">
-        <v>6.3424407303283705E-10</v>
+        <v>9.6594583892903297E-8</v>
+      </c>
+      <c r="I47">
+        <v>0.75904434850000002</v>
       </c>
       <c r="T47" t="s">
         <v>39</v>
@@ -14710,38 +15445,41 @@
       </c>
       <c r="B48">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>6.8928110932124101E-2</v>
       </c>
       <c r="C48" s="3">
         <f t="shared" si="2"/>
-        <v>44776.000694444447</v>
+        <v>44776.625694444447</v>
       </c>
       <c r="E48" s="1">
         <v>44776.146527777775</v>
       </c>
       <c r="F48" s="2">
-        <v>6.1770763270172503E-10</v>
+        <v>1.00749518391823E-7</v>
       </c>
       <c r="G48" s="2">
-        <v>4.0783672234896999E-10</v>
+        <v>6.65190960647415E-8</v>
       </c>
       <c r="H48" s="2">
-        <v>4.0384717270957802E-10</v>
+        <v>6.5868391454465701E-8</v>
+      </c>
+      <c r="I48">
+        <v>0.67891565050000002</v>
       </c>
       <c r="T48" t="s">
         <v>40</v>
       </c>
       <c r="U48" s="2">
         <f>B46</f>
-        <v>0</v>
+        <v>8.8538283179216595E-2</v>
       </c>
       <c r="V48" s="2">
         <f>B47</f>
-        <v>0</v>
+        <v>6.8701391389362806E-2</v>
       </c>
       <c r="W48" s="2">
         <f>B48</f>
-        <v>0</v>
+        <v>6.8928110932124101E-2</v>
       </c>
       <c r="Y48">
         <v>0.108402639333512</v>
@@ -14760,38 +15498,41 @@
       </c>
       <c r="B49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.364117442712454</v>
       </c>
       <c r="C49" s="3">
         <f t="shared" si="2"/>
-        <v>44776.000694444447</v>
+        <v>44776.625694444447</v>
       </c>
       <c r="E49" s="1">
         <v>44776.156944444447</v>
       </c>
       <c r="F49" s="2">
-        <v>6.6201536184373002E-10</v>
+        <v>1.05944141049072E-7</v>
       </c>
       <c r="G49" s="2">
-        <v>4.66962373632692E-10</v>
+        <v>7.4729274315264904E-8</v>
       </c>
       <c r="H49" s="2">
-        <v>4.5209966933268698E-10</v>
+        <v>7.2350754825156606E-8</v>
+      </c>
+      <c r="I49">
+        <v>0.70024108200000001</v>
       </c>
       <c r="T49" t="s">
         <v>41</v>
       </c>
       <c r="U49" s="2">
         <f>B49</f>
-        <v>0</v>
+        <v>0.364117442712454</v>
       </c>
       <c r="V49" s="2">
         <f>B50</f>
-        <v>0</v>
+        <v>0.246683535248926</v>
       </c>
       <c r="W49" s="2">
         <f>B51</f>
-        <v>0</v>
+        <v>0.25086465947329001</v>
       </c>
       <c r="Y49">
         <v>0.43361055733404802</v>
@@ -14810,38 +15551,41 @@
       </c>
       <c r="B50">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.246683535248926</v>
       </c>
       <c r="C50" s="3">
         <f t="shared" si="2"/>
-        <v>44776.000694444447</v>
+        <v>44776.625694444447</v>
       </c>
       <c r="E50" s="1">
         <v>44776.167361111111</v>
       </c>
       <c r="F50" s="2">
-        <v>8.0323787221929904E-10</v>
+        <v>1.24184369088094E-7</v>
       </c>
       <c r="G50" s="2">
-        <v>5.92647323868018E-10</v>
+        <v>9.1626075600631999E-8</v>
       </c>
       <c r="H50" s="2">
-        <v>5.8212743970692898E-10</v>
+        <v>8.9999651819504605E-8</v>
+      </c>
+      <c r="I50">
+        <v>0.740701163</v>
       </c>
       <c r="T50" t="s">
         <v>42</v>
       </c>
       <c r="U50" s="2">
         <f>B52</f>
-        <v>0.169640190738721</v>
+        <v>1.45646977084981</v>
       </c>
       <c r="V50" s="2">
         <f>B53</f>
-        <v>0.15434875599756201</v>
+        <v>0.96474323456365096</v>
       </c>
       <c r="W50" s="2">
         <f>B54</f>
-        <v>0.15477545698098</v>
+        <v>0.98707974061158099</v>
       </c>
       <c r="Y50">
         <v>2.3259290609915499</v>
@@ -14860,38 +15604,41 @@
       </c>
       <c r="B51">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.25086465947329001</v>
       </c>
       <c r="C51" s="3">
         <f t="shared" si="2"/>
-        <v>44776.000694444447</v>
+        <v>44776.625694444447</v>
       </c>
       <c r="E51" s="1">
         <v>44776.177777777775</v>
       </c>
       <c r="F51" s="2">
-        <v>8.9163950421949099E-10</v>
+        <v>1.37878724988046E-7</v>
       </c>
       <c r="G51" s="2">
-        <v>5.8876469747462296E-10</v>
+        <v>9.1043662179332501E-8</v>
       </c>
       <c r="H51" s="2">
-        <v>5.7397606382619397E-10</v>
+        <v>8.8756820982546494E-8</v>
+      </c>
+      <c r="I51">
+        <v>0.74046465699999997</v>
       </c>
       <c r="T51" t="s">
         <v>43</v>
       </c>
       <c r="U51" s="2">
         <f>B55</f>
-        <v>0.77298920549835903</v>
+        <v>5.8258790833992702</v>
       </c>
       <c r="V51" s="2">
         <f>B56</f>
-        <v>0.59065830904028005</v>
+        <v>3.8589729382545999</v>
       </c>
       <c r="W51" s="2">
         <f>B57</f>
-        <v>0.58248755947293596</v>
+        <v>3.94831896244632</v>
       </c>
       <c r="Y51">
         <v>9.3037162439662104</v>
@@ -14910,38 +15657,41 @@
       </c>
       <c r="B52" s="5">
         <f t="shared" si="1"/>
-        <v>0.169640190738721</v>
+        <v>1.45646977084981</v>
       </c>
       <c r="C52" s="6">
         <f t="shared" si="2"/>
-        <v>44776.636111111111</v>
+        <v>44776.625694444447</v>
       </c>
       <c r="E52" s="1">
         <v>44776.188194444447</v>
       </c>
       <c r="F52" s="2">
-        <v>7.8059713555551002E-10</v>
+        <v>1.19886430033326E-7</v>
       </c>
       <c r="G52" s="2">
-        <v>5.88856603044077E-10</v>
+        <v>9.0438348701767694E-8</v>
       </c>
       <c r="H52" s="2">
-        <v>5.8515172826811804E-10</v>
+        <v>8.9869343015544797E-8</v>
+      </c>
+      <c r="I52">
+        <v>0.74873955049999996</v>
       </c>
       <c r="T52" t="s">
         <v>44</v>
       </c>
       <c r="U52" s="2">
         <f>B58</f>
-        <v>3.0919568219934299</v>
+        <v>23.303516333596999</v>
       </c>
       <c r="V52" s="2">
         <f>B59</f>
-        <v>2.3626332361611202</v>
+        <v>15.435891753018399</v>
       </c>
       <c r="W52" s="2">
         <f>B60</f>
-        <v>2.3299502378917398</v>
+        <v>15.793275849785299</v>
       </c>
       <c r="Y52">
         <v>37.214864975864799</v>
@@ -14960,23 +15710,26 @@
       </c>
       <c r="B53" s="5">
         <f t="shared" si="1"/>
-        <v>0.15434875599756201</v>
+        <v>0.96474323456365096</v>
       </c>
       <c r="C53" s="6">
         <f t="shared" si="2"/>
-        <v>44776.636111111111</v>
+        <v>44776.625694444447</v>
       </c>
       <c r="E53" s="1">
         <v>44776.198611111111</v>
       </c>
       <c r="F53" s="2">
-        <v>8.1405890757249299E-10</v>
+        <v>1.2609225603872499E-7</v>
       </c>
       <c r="G53" s="2">
-        <v>5.1738292916028E-10</v>
+        <v>8.0139140013971602E-8</v>
       </c>
       <c r="H53" s="2">
-        <v>5.11387904601465E-10</v>
+        <v>7.9210550984000096E-8</v>
+      </c>
+      <c r="I53">
+        <v>0.73845619600000001</v>
       </c>
     </row>
     <row r="54" spans="1:27" x14ac:dyDescent="0.25">
@@ -14986,23 +15739,26 @@
       </c>
       <c r="B54" s="5">
         <f t="shared" si="1"/>
-        <v>0.15477545698098</v>
+        <v>0.98707974061158099</v>
       </c>
       <c r="C54" s="6">
         <f t="shared" si="2"/>
-        <v>44776.636111111111</v>
+        <v>44776.625694444447</v>
       </c>
       <c r="E54" s="1">
         <v>44776.209027777775</v>
       </c>
       <c r="F54" s="2">
-        <v>7.7083428546008703E-10</v>
+        <v>1.20592636157517E-7</v>
       </c>
       <c r="G54" s="2">
-        <v>5.1529120463564605E-10</v>
+        <v>8.0614375783670403E-8</v>
       </c>
       <c r="H54" s="2">
-        <v>4.9604013721892498E-10</v>
+        <v>7.7602655868289506E-8</v>
+      </c>
+      <c r="I54">
+        <v>0.726575334499999</v>
       </c>
     </row>
     <row r="55" spans="1:27" x14ac:dyDescent="0.25">
@@ -15012,23 +15768,26 @@
       </c>
       <c r="B55" s="5">
         <f t="shared" si="1"/>
-        <v>0.77298920549835903</v>
+        <v>5.8258790833992702</v>
       </c>
       <c r="C55" s="6">
         <f t="shared" si="2"/>
-        <v>44776.636111111111</v>
+        <v>44776.625694444447</v>
       </c>
       <c r="E55" s="1">
         <v>44776.219444444447</v>
       </c>
       <c r="F55" s="2">
-        <v>9.9394579461837903E-10</v>
+        <v>1.4862872126020399E-7</v>
       </c>
       <c r="G55" s="2">
-        <v>6.6814915093842095E-10</v>
+        <v>9.9911035846152306E-8</v>
       </c>
       <c r="H55" s="2">
-        <v>6.6922468618957803E-10</v>
+        <v>1.00071864968304E-7</v>
+      </c>
+      <c r="I55">
+        <v>0.78202204350000004</v>
       </c>
     </row>
     <row r="56" spans="1:27" x14ac:dyDescent="0.25">
@@ -15038,23 +15797,26 @@
       </c>
       <c r="B56" s="5">
         <f t="shared" si="1"/>
-        <v>0.59065830904028005</v>
+        <v>3.8589729382545999</v>
       </c>
       <c r="C56" s="6">
         <f t="shared" si="2"/>
-        <v>44776.636111111111</v>
+        <v>44776.625694444447</v>
       </c>
       <c r="E56" s="1">
         <v>44776.229861111111</v>
       </c>
       <c r="F56" s="2">
-        <v>1.2167593713498799E-9</v>
+        <v>1.7464465475407299E-7</v>
       </c>
       <c r="G56" s="2">
-        <v>8.8406100913321904E-10</v>
+        <v>1.2689158872093E-7</v>
       </c>
       <c r="H56" s="2">
-        <v>8.5683742196982795E-10</v>
+        <v>1.2298411605744001E-7</v>
+      </c>
+      <c r="I56">
+        <v>0.83594533650000002</v>
       </c>
     </row>
     <row r="57" spans="1:27" x14ac:dyDescent="0.25">
@@ -15064,23 +15826,26 @@
       </c>
       <c r="B57" s="5">
         <f t="shared" si="1"/>
-        <v>0.58248755947293596</v>
+        <v>3.94831896244632</v>
       </c>
       <c r="C57" s="6">
         <f t="shared" si="2"/>
-        <v>44776.636111111111</v>
+        <v>44776.625694444447</v>
       </c>
       <c r="E57" s="1">
         <v>44776.240277777775</v>
       </c>
       <c r="F57" s="2">
-        <v>9.9761659609293507E-10</v>
+        <v>1.49384516203063E-7</v>
       </c>
       <c r="G57" s="2">
-        <v>6.6604720288510995E-10</v>
+        <v>9.9734847598926806E-8</v>
       </c>
       <c r="H57" s="2">
-        <v>6.48865689616417E-10</v>
+        <v>9.7162063567462706E-8</v>
+      </c>
+      <c r="I57">
+        <v>0.78025976949999998</v>
       </c>
     </row>
     <row r="58" spans="1:27" x14ac:dyDescent="0.25">
@@ -15090,23 +15855,26 @@
       </c>
       <c r="B58" s="5">
         <f t="shared" si="1"/>
-        <v>3.0919568219934299</v>
+        <v>23.303516333596999</v>
       </c>
       <c r="C58" s="6">
         <f t="shared" si="2"/>
-        <v>44776.636111111111</v>
+        <v>44776.625694444447</v>
       </c>
       <c r="E58" s="1">
         <v>44776.250694444447</v>
       </c>
       <c r="F58" s="2">
-        <v>8.6240978978739599E-10</v>
+        <v>1.31607155934079E-7</v>
       </c>
       <c r="G58" s="2">
-        <v>5.8611970716859301E-10</v>
+        <v>8.9444193016331499E-8</v>
       </c>
       <c r="H58" s="2">
-        <v>5.8022196753551605E-10</v>
+        <v>8.8544174547710997E-8</v>
+      </c>
+      <c r="I58">
+        <v>0.75657462549999999</v>
       </c>
     </row>
     <row r="59" spans="1:27" x14ac:dyDescent="0.25">
@@ -15116,23 +15884,26 @@
       </c>
       <c r="B59" s="5">
         <f t="shared" si="1"/>
-        <v>2.3626332361611202</v>
+        <v>15.435891753018399</v>
       </c>
       <c r="C59" s="6">
         <f t="shared" si="2"/>
-        <v>44776.636111111111</v>
+        <v>44776.625694444447</v>
       </c>
       <c r="E59" s="1">
         <v>44776.261111111111</v>
       </c>
       <c r="F59" s="2">
-        <v>6.2067528552950298E-10</v>
+        <v>9.9090210221863701E-8</v>
       </c>
       <c r="G59" s="2">
-        <v>4.3424020476832302E-10</v>
+        <v>6.9326029535019303E-8</v>
       </c>
       <c r="H59" s="2">
-        <v>4.2592079278639002E-10</v>
+        <v>6.7997843442912401E-8</v>
+      </c>
+      <c r="I59">
+        <v>0.70298291499999999</v>
       </c>
     </row>
     <row r="60" spans="1:27" x14ac:dyDescent="0.25">
@@ -15142,23 +15913,26 @@
       </c>
       <c r="B60" s="5">
         <f t="shared" si="1"/>
-        <v>2.3299502378917398</v>
+        <v>15.793275849785299</v>
       </c>
       <c r="C60" s="6">
         <f>_xlfn.XLOOKUP(MAX(B28:CS28), B28:CS28, $B$1:$CS$1)</f>
-        <v>44776.636111111111</v>
+        <v>44776.625694444447</v>
       </c>
       <c r="E60" s="1">
         <v>44776.271527777775</v>
       </c>
       <c r="F60" s="2">
-        <v>5.4594806038022402E-10</v>
+        <v>8.8754463725521903E-8</v>
       </c>
       <c r="G60" s="2">
-        <v>3.8182657244080302E-10</v>
+        <v>6.2073327359061195E-8</v>
       </c>
       <c r="H60" s="2">
-        <v>3.7585111632660001E-10</v>
+        <v>6.1101900878412694E-8</v>
+      </c>
+      <c r="I60">
+        <v>0.68254177999999999</v>
       </c>
     </row>
     <row r="61" spans="1:27" x14ac:dyDescent="0.25">
@@ -15177,13 +15951,16 @@
         <v>44776.281944444447</v>
       </c>
       <c r="F61" s="2">
-        <v>5.2090447587157199E-10</v>
+        <v>8.4536834987216905E-8</v>
       </c>
       <c r="G61" s="2">
-        <v>3.7292213053298599E-10</v>
+        <v>6.0520993909596605E-8</v>
       </c>
       <c r="H61" s="2">
-        <v>3.6676338273875602E-10</v>
+        <v>5.95214996260397E-8</v>
+      </c>
+      <c r="I61">
+        <v>0.684465781</v>
       </c>
     </row>
     <row r="62" spans="1:27" x14ac:dyDescent="0.25">
@@ -15192,23 +15969,26 @@
       </c>
       <c r="B62" s="7">
         <f>MAX(B30:CS30)</f>
-        <v>4.2447373637128996</v>
+        <v>9.6829050148094105</v>
       </c>
       <c r="C62" s="6">
         <f t="shared" si="4"/>
-        <v>44776.636111111111</v>
+        <v>44776.625694444447</v>
       </c>
       <c r="E62" s="1">
         <v>44776.292361111111</v>
       </c>
       <c r="F62" s="2">
-        <v>5.8306301614118296E-10</v>
+        <v>9.37925917280448E-8</v>
       </c>
       <c r="G62" s="2">
-        <v>4.0947433337382098E-10</v>
+        <v>6.5868796186162205E-8</v>
       </c>
       <c r="H62" s="2">
-        <v>3.9646036096304999E-10</v>
+        <v>6.3775344592046203E-8</v>
+      </c>
+      <c r="I62">
+        <v>0.69437548549999994</v>
       </c>
     </row>
     <row r="63" spans="1:27" x14ac:dyDescent="0.25">
@@ -15218,13 +15998,16 @@
         <v>44776.302777777775</v>
       </c>
       <c r="F63" s="2">
-        <v>6.8948522561471099E-10</v>
+        <v>1.10005014672529E-7</v>
       </c>
       <c r="G63" s="2">
-        <v>4.2537444364903198E-10</v>
+        <v>6.7867040767186004E-8</v>
       </c>
       <c r="H63" s="2">
-        <v>4.1509363568013599E-10</v>
+        <v>6.6226772943665902E-8</v>
+      </c>
+      <c r="I63">
+        <v>0.7037178785</v>
       </c>
     </row>
     <row r="64" spans="1:27" x14ac:dyDescent="0.25">
@@ -15232,876 +16015,1062 @@
         <v>44776.313194444447</v>
       </c>
       <c r="F64" s="2">
-        <v>4.5233308144590302E-10</v>
+        <v>7.42269507867231E-8</v>
       </c>
       <c r="G64" s="2">
-        <v>3.3617646604093302E-10</v>
+        <v>5.5165883337354401E-8</v>
       </c>
       <c r="H64" s="2">
-        <v>3.32905053105935E-10</v>
+        <v>5.4629051040995798E-8</v>
+      </c>
+      <c r="I64">
+        <v>0.672222341</v>
       </c>
     </row>
-    <row r="65" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E65" s="1">
         <v>44776.323611111111</v>
       </c>
       <c r="F65" s="2">
-        <v>5.1388836432907001E-10</v>
+        <v>8.37489976291492E-8</v>
       </c>
       <c r="G65" s="2">
-        <v>3.6202863176049598E-10</v>
+        <v>5.9000236484766003E-8</v>
       </c>
       <c r="H65" s="2">
-        <v>3.5559226663422601E-10</v>
+        <v>5.7951294409898098E-8</v>
+      </c>
+      <c r="I65">
+        <v>0.67980481400000004</v>
       </c>
     </row>
-    <row r="66" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E66" s="1">
         <v>44776.334027777775</v>
       </c>
       <c r="F66" s="2">
-        <v>8.7150875242922001E-10</v>
+        <v>1.3456036196529701E-7</v>
       </c>
       <c r="G66" s="2">
-        <v>5.5160123399840004E-10</v>
+        <v>8.5166857477847597E-8</v>
       </c>
       <c r="H66" s="2">
-        <v>5.4487477046016601E-10</v>
+        <v>8.41282960556246E-8</v>
+      </c>
+      <c r="I66">
+        <v>0.74230587949999904</v>
       </c>
     </row>
-    <row r="67" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E67" s="1">
         <v>44776.344444444447</v>
       </c>
       <c r="F67" s="2">
-        <v>8.5961704616773898E-10</v>
+        <v>1.3044573565671401E-7</v>
       </c>
       <c r="G67" s="2">
-        <v>6.0404134311816401E-10</v>
+        <v>9.1662464954226799E-8</v>
       </c>
       <c r="H67" s="2">
-        <v>5.8966330620128902E-10</v>
+        <v>8.9480617106329296E-8</v>
+      </c>
+      <c r="I67">
+        <v>0.76352864149999999</v>
       </c>
     </row>
-    <row r="68" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E68" s="1">
         <v>44776.354861111111</v>
       </c>
       <c r="F68" s="2">
-        <v>6.8942732597906497E-10</v>
+        <v>1.0828443230519701E-7</v>
       </c>
       <c r="G68" s="2">
-        <v>4.5900594760520299E-10</v>
+        <v>7.20934558107596E-8</v>
       </c>
       <c r="H68" s="2">
-        <v>4.40987573149627E-10</v>
+        <v>6.9263412127430206E-8</v>
+      </c>
+      <c r="I68">
+        <v>0.72191215399999997</v>
       </c>
     </row>
-    <row r="69" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E69" s="1">
         <v>44776.365277777775</v>
       </c>
       <c r="F69" s="2">
-        <v>6.2702083736231303E-10</v>
+        <v>9.84825997732359E-8</v>
       </c>
       <c r="G69" s="2">
-        <v>4.6460794079042198E-10</v>
+        <v>7.2973329046067995E-8</v>
       </c>
       <c r="H69" s="2">
-        <v>4.5915625771288198E-10</v>
+        <v>7.2117064164911005E-8</v>
+      </c>
+      <c r="I69">
+        <v>0.72191215399999997</v>
       </c>
     </row>
-    <row r="70" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E70" s="1">
         <v>44776.375694444447</v>
       </c>
       <c r="F70" s="2">
-        <v>8.5293857979288797E-10</v>
+        <v>1.2803878825587399E-7</v>
       </c>
       <c r="G70" s="2">
-        <v>6.6496900461993103E-10</v>
+        <v>9.9821754575454596E-8</v>
       </c>
       <c r="H70" s="2">
-        <v>6.3493447019437199E-10</v>
+        <v>9.5313123490926E-8</v>
+      </c>
+      <c r="I70">
+        <v>0.77710206100000001</v>
       </c>
     </row>
-    <row r="71" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E71" s="1">
         <v>44776.386111111111</v>
       </c>
       <c r="F71" s="2">
-        <v>8.1528735054230495E-10</v>
+        <v>1.2629784050930401E-7</v>
       </c>
       <c r="G71" s="2">
-        <v>5.6304335255230795E-10</v>
+        <v>8.7222203919932196E-8</v>
       </c>
       <c r="H71" s="2">
-        <v>5.5045012158756103E-10</v>
+        <v>8.5271360606545198E-8</v>
+      </c>
+      <c r="I71">
+        <v>0.73831050949999999</v>
       </c>
     </row>
-    <row r="72" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E72" s="1">
         <v>44776.396527777775</v>
       </c>
       <c r="F72" s="2">
-        <v>5.0022108606043999E-10</v>
+        <v>8.3491559530010094E-8</v>
       </c>
       <c r="G72" s="2">
-        <v>3.3192733722912098E-10</v>
+        <v>5.5401764956497602E-8</v>
       </c>
       <c r="H72" s="2">
-        <v>3.1403445702283099E-10</v>
+        <v>5.2415276552998997E-8</v>
+      </c>
+      <c r="I72">
+        <v>0.65388842250000001</v>
       </c>
     </row>
-    <row r="73" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E73" s="1">
         <v>44776.406944444447</v>
       </c>
       <c r="F73" s="2">
-        <v>4.6844564912095302E-10</v>
+        <v>7.7510850378197098E-8</v>
       </c>
       <c r="G73" s="2">
-        <v>3.3981300122528198E-10</v>
+        <v>5.6226789050408003E-8</v>
       </c>
       <c r="H73" s="2">
-        <v>3.3049676507131203E-10</v>
+        <v>5.4685288157373297E-8</v>
+      </c>
+      <c r="I73">
+        <v>0.66321230600000003</v>
       </c>
     </row>
-    <row r="74" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E74" s="1">
         <v>44776.417361111111</v>
       </c>
       <c r="F74" s="2">
-        <v>9.4067720518393391E-10</v>
+        <v>1.45550665327585E-7</v>
       </c>
       <c r="G74" s="2">
-        <v>5.9749891916897197E-10</v>
+        <v>9.2450805376652304E-8</v>
       </c>
       <c r="H74" s="2">
-        <v>5.7387604940369601E-10</v>
+        <v>8.8795646739425097E-8</v>
+      </c>
+      <c r="I74">
+        <v>0.73972780449999997</v>
       </c>
     </row>
-    <row r="75" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E75" s="1">
         <v>44776.427777777775</v>
       </c>
       <c r="F75" s="2">
-        <v>6.5682430527547602E-10</v>
+        <v>1.03039015709554E-7</v>
       </c>
       <c r="G75" s="2">
-        <v>4.9117454685511605E-10</v>
+        <v>7.7052784807964101E-8</v>
       </c>
       <c r="H75" s="2">
-        <v>4.8591189854669703E-10</v>
+        <v>7.6227209236170099E-8</v>
+      </c>
+      <c r="I75">
+        <v>0.72333429699999996</v>
       </c>
     </row>
-    <row r="76" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E76" s="1">
         <v>44776.438194444447</v>
       </c>
       <c r="F76" s="2">
-        <v>6.3892786223280001E-10</v>
+        <v>1.0138129644085801E-7</v>
       </c>
       <c r="G76" s="2">
-        <v>4.3201938664700999E-10</v>
+        <v>6.8550282581515004E-8</v>
       </c>
       <c r="H76" s="2">
-        <v>4.2364331779199299E-10</v>
+        <v>6.7221217486965405E-8</v>
+      </c>
+      <c r="I76">
+        <v>0.71002781749999999</v>
       </c>
     </row>
-    <row r="77" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E77" s="1">
         <v>44776.448611111111</v>
       </c>
       <c r="F77" s="2">
-        <v>7.1708642457303E-10</v>
+        <v>1.11984058743973E-7</v>
       </c>
       <c r="G77" s="2">
-        <v>4.9142552613458E-10</v>
+        <v>7.6743643584538195E-8</v>
       </c>
       <c r="H77" s="2">
-        <v>4.7921129578899002E-10</v>
+        <v>7.4836203919844605E-8</v>
+      </c>
+      <c r="I77">
+        <v>0.72868923050000001</v>
       </c>
     </row>
-    <row r="78" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E78" s="1">
         <v>44776.459027777775</v>
       </c>
       <c r="F78" s="2">
-        <v>4.5867702983181802E-10</v>
+        <v>7.5515919884758005E-8</v>
       </c>
       <c r="G78" s="2">
-        <v>3.36586100920068E-10</v>
+        <v>5.5415046706262998E-8</v>
       </c>
       <c r="H78" s="2">
-        <v>3.2110161961366301E-10</v>
+        <v>5.2865704198383603E-8</v>
+      </c>
+      <c r="I78">
+        <v>0.66863318549999995</v>
       </c>
     </row>
-    <row r="79" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E79" s="1">
         <v>44776.469444444447</v>
       </c>
       <c r="F79" s="2">
-        <v>5.3868177925949697E-10</v>
+        <v>8.9569897468822199E-8</v>
       </c>
       <c r="G79" s="2">
-        <v>3.2487796769969299E-10</v>
+        <v>5.4019436663800003E-8</v>
       </c>
       <c r="H79" s="2">
-        <v>3.1234882234302598E-10</v>
+        <v>5.1936139422548101E-8</v>
+      </c>
+      <c r="I79">
+        <v>0.65794700399999995</v>
       </c>
     </row>
-    <row r="80" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E80" s="1">
         <v>44776.479861111111</v>
       </c>
       <c r="F80" s="2">
-        <v>6.1779634236488301E-10</v>
+        <v>9.9278824374308606E-8</v>
       </c>
       <c r="G80" s="2">
-        <v>4.3302363931941802E-10</v>
+        <v>6.9586164386871801E-8</v>
       </c>
       <c r="H80" s="2">
-        <v>4.2005611076522498E-10</v>
+        <v>6.7502304541728903E-8</v>
+      </c>
+      <c r="I80">
+        <v>0.69552619199999999</v>
       </c>
     </row>
-    <row r="81" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E81" s="1">
         <v>44776.490277777775</v>
       </c>
       <c r="F81" s="2">
-        <v>7.3499520574830097E-10</v>
+        <v>1.1433540602737001E-7</v>
       </c>
       <c r="G81" s="2">
-        <v>4.9935639501594296E-10</v>
+        <v>7.7679576315849496E-8</v>
       </c>
       <c r="H81" s="2">
-        <v>4.8157476699739597E-10</v>
+        <v>7.4913477103605801E-8</v>
+      </c>
+      <c r="I81">
+        <v>0.73331566249999902</v>
       </c>
     </row>
-    <row r="82" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E82" s="1">
         <v>44776.500694444447</v>
       </c>
       <c r="F82" s="2">
-        <v>9.4909688375402305E-10</v>
+        <v>1.45994317995278E-7</v>
       </c>
       <c r="G82" s="2">
-        <v>5.4693488119704999E-10</v>
+        <v>8.4131964117135899E-8</v>
       </c>
       <c r="H82" s="2">
-        <v>5.4129356190608701E-10</v>
+        <v>8.3264191209349899E-8</v>
+      </c>
+      <c r="I82">
+        <v>0.74682702999999995</v>
       </c>
     </row>
-    <row r="83" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E83" s="1">
         <v>44776.511111111111</v>
       </c>
       <c r="F83" s="2">
-        <v>8.8232007600894004E-10</v>
+        <v>1.3323298366791201E-7</v>
       </c>
       <c r="G83" s="2">
-        <v>6.2229837965693897E-10</v>
+        <v>9.3968925913969705E-8</v>
       </c>
       <c r="H83" s="2">
-        <v>6.0296341797469096E-10</v>
+        <v>9.1049288581031497E-8</v>
+      </c>
+      <c r="I83">
+        <v>0.76967573</v>
       </c>
     </row>
-    <row r="84" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E84" s="1">
         <v>44776.521527777775</v>
       </c>
       <c r="F84" s="2">
-        <v>8.3121502177750504E-10</v>
+        <v>1.27761173164764E-7</v>
       </c>
       <c r="G84" s="2">
-        <v>5.72337455465218E-10</v>
+        <v>8.7970624737456199E-8</v>
       </c>
       <c r="H84" s="2">
-        <v>5.6222679339298403E-10</v>
+        <v>8.6416574325402399E-8</v>
+      </c>
+      <c r="I84">
+        <v>0.7477791265</v>
       </c>
     </row>
-    <row r="85" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E85" s="1">
         <v>44776.531944444447</v>
       </c>
       <c r="F85" s="2">
-        <v>7.5270898989416299E-10</v>
+        <v>1.18594503912163E-7</v>
       </c>
       <c r="G85" s="2">
-        <v>4.6951422905553096E-10</v>
+        <v>7.3975211962877299E-8</v>
       </c>
       <c r="H85" s="2">
-        <v>4.5207957754548799E-10</v>
+        <v>7.1228262113146997E-8</v>
+      </c>
+      <c r="I85">
+        <v>0.71824162000000003</v>
       </c>
     </row>
-    <row r="86" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E86" s="1">
         <v>44776.542361111111</v>
       </c>
       <c r="F86" s="2">
-        <v>8.2191583823346199E-10</v>
+        <v>1.2827286419484501E-7</v>
       </c>
       <c r="G86" s="2">
-        <v>4.7835593819346598E-10</v>
+        <v>7.4654950597264206E-8</v>
       </c>
       <c r="H86" s="2">
-        <v>4.5925559701541398E-10</v>
+        <v>7.1674042631118694E-8</v>
+      </c>
+      <c r="I86">
+        <v>0.72944691949999996</v>
       </c>
     </row>
-    <row r="87" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E87" s="1">
         <v>44776.552777777775</v>
       </c>
       <c r="F87" s="2">
-        <v>5.0678380596177797E-10</v>
+        <v>8.2552067113168302E-8</v>
       </c>
       <c r="G87" s="2">
-        <v>3.7062344732674202E-10</v>
+        <v>6.0372354715777496E-8</v>
       </c>
       <c r="H87" s="2">
-        <v>3.6105742678704099E-10</v>
+        <v>5.8814106879375399E-8</v>
+      </c>
+      <c r="I87">
+        <v>0.68032893350000001</v>
       </c>
     </row>
-    <row r="88" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E88" s="1">
         <v>44776.563194444447</v>
       </c>
       <c r="F88" s="2">
-        <v>3.2699546023203698E-10</v>
+        <v>5.6289250569251201E-8</v>
       </c>
       <c r="G88" s="2">
-        <v>2.4640797211936901E-10</v>
+        <v>4.2416858249319797E-8</v>
       </c>
       <c r="H88" s="2">
-        <v>2.4415170671318801E-10</v>
+        <v>4.2028462983332902E-8</v>
+      </c>
+      <c r="I88">
+        <v>0.62184915699999999</v>
       </c>
     </row>
-    <row r="89" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E89" s="1">
         <v>44776.573611111111</v>
       </c>
       <c r="F89" s="2">
-        <v>4.72004980013671E-10</v>
+        <v>8.0481383774328897E-8</v>
       </c>
       <c r="G89" s="2">
-        <v>2.5879797023507401E-10</v>
+        <v>4.4127540268418999E-8</v>
       </c>
       <c r="H89" s="2">
-        <v>2.5964474180386499E-10</v>
+        <v>4.4271922955657401E-8</v>
+      </c>
+      <c r="I89">
+        <v>0.63156217000000003</v>
       </c>
     </row>
-    <row r="90" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E90" s="1">
         <v>44776.584027777775</v>
       </c>
       <c r="F90" s="2">
-        <v>5.4989495226542702E-10</v>
+        <v>9.0839956727602702E-8</v>
       </c>
       <c r="G90" s="2">
-        <v>3.2574195123283501E-10</v>
+        <v>5.3810977227716901E-8</v>
       </c>
       <c r="H90" s="2">
-        <v>3.1320516852857797E-10</v>
+        <v>5.1739962039249402E-8</v>
+      </c>
+      <c r="I90">
+        <v>0.66496995749999999</v>
       </c>
     </row>
-    <row r="91" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E91" s="1">
         <v>44776.594444444447</v>
       </c>
       <c r="F91" s="2">
-        <v>6.6930170633289299E-10</v>
+        <v>1.0987121629035801E-7</v>
       </c>
       <c r="G91" s="2">
-        <v>3.87628032659233E-10</v>
+        <v>6.3632234929052404E-8</v>
       </c>
       <c r="H91" s="2">
-        <v>3.7411529757028501E-10</v>
+        <v>6.1414011629415794E-8</v>
+      </c>
+      <c r="I91">
+        <v>0.67182250649999997</v>
       </c>
     </row>
-    <row r="92" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E92" s="1">
         <v>44776.604861111111</v>
       </c>
       <c r="F92" s="2">
-        <v>1.0489946937872801E-9</v>
+        <v>1.6818201192618799E-7</v>
       </c>
       <c r="G92" s="2">
-        <v>4.89366799657478E-10</v>
+        <v>7.8458636089864999E-8</v>
       </c>
       <c r="H92" s="2">
-        <v>4.7535055831767803E-10</v>
+        <v>7.6211456307944803E-8</v>
+      </c>
+      <c r="I92">
+        <v>0.69815132099999999</v>
       </c>
     </row>
-    <row r="93" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E93" s="1">
         <v>44776.615277777775</v>
       </c>
       <c r="F93" s="2">
-        <v>2.3911052353288801E-8</v>
+        <v>2.59925867337766E-6</v>
       </c>
       <c r="G93" s="2">
-        <v>1.38580466497013E-8</v>
+        <v>1.5064434394438E-6</v>
       </c>
       <c r="H93" s="2">
-        <v>1.35726525047815E-8</v>
+        <v>1.4754195766852299E-6</v>
+      </c>
+      <c r="I93">
+        <v>1.3141996124999999</v>
       </c>
     </row>
-    <row r="94" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E94" s="1">
         <v>44776.625694444447</v>
       </c>
       <c r="F94">
-        <v>8.4256581576265999E-4</v>
+        <v>2.2757340169528399E-2</v>
       </c>
       <c r="G94">
-        <v>5.5810267175125205E-4</v>
+        <v>1.5074113040056999E-2</v>
       </c>
       <c r="H94">
-        <v>5.7102431065263301E-4</v>
+        <v>1.5423120947055899E-2</v>
+      </c>
+      <c r="I94">
+        <v>12.6789259225</v>
       </c>
     </row>
-    <row r="95" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E95" s="1">
         <v>44776.636111111111</v>
       </c>
       <c r="F95">
-        <v>3.0194890839779602E-3</v>
+        <v>6.88792344191058E-3</v>
       </c>
       <c r="G95">
-        <v>2.30725901968859E-3</v>
+        <v>5.2632160762136997E-3</v>
       </c>
       <c r="H95">
-        <v>2.27534202919115E-3</v>
+        <v>5.1904084650772203E-3</v>
+      </c>
+      <c r="I95">
+        <v>22.620213794999898</v>
       </c>
     </row>
-    <row r="96" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E96" s="1">
         <v>44776.646527777775</v>
       </c>
       <c r="F96">
-        <v>1.3419280710164001E-3</v>
+        <v>5.7579781162764004E-3</v>
       </c>
       <c r="G96">
-        <v>1.00295106012561E-3</v>
+        <v>4.3034871843328102E-3</v>
       </c>
       <c r="H96">
-        <v>9.900025355164409E-4</v>
+        <v>4.2479273350382804E-3</v>
+      </c>
+      <c r="I96">
+        <v>19.508647905</v>
       </c>
     </row>
-    <row r="97" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="97" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E97" s="1">
         <v>44776.656944444447</v>
       </c>
       <c r="F97">
-        <v>4.3902523980032999E-4</v>
+        <v>5.4595327590182402E-3</v>
       </c>
       <c r="G97">
-        <v>3.0019692886353901E-4</v>
+        <v>3.73312242376734E-3</v>
       </c>
       <c r="H97">
-        <v>2.9503740515731899E-4</v>
+        <v>3.6689607626336899E-3</v>
+      </c>
+      <c r="I97">
+        <v>15.20489341</v>
       </c>
     </row>
-    <row r="98" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="98" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E98" s="1">
         <v>44776.667361111111</v>
       </c>
       <c r="F98">
-        <v>6.5939852060204699E-4</v>
+        <v>4.8759650107001798E-3</v>
       </c>
       <c r="G98">
-        <v>5.1861207800330098E-4</v>
+        <v>3.8349105547707601E-3</v>
       </c>
       <c r="H98">
-        <v>5.1401979061092601E-4</v>
+        <v>3.8009525886131702E-3</v>
+      </c>
+      <c r="I98">
+        <v>17.173613769999999</v>
       </c>
     </row>
-    <row r="99" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="99" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E99" s="1">
         <v>44776.677777777775</v>
       </c>
       <c r="F99">
-        <v>1.3813185597794501E-3</v>
+        <v>5.4686815441540304E-3</v>
       </c>
       <c r="G99">
-        <v>1.0531266020267699E-3</v>
+        <v>4.1693597551748099E-3</v>
       </c>
       <c r="H99">
-        <v>1.0334830346720399E-3</v>
+        <v>4.0915902838031598E-3</v>
+      </c>
+      <c r="I99">
+        <v>19.879890565</v>
       </c>
     </row>
-    <row r="100" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="100" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E100" s="1">
         <v>44776.688194444447</v>
       </c>
       <c r="F100">
-        <v>9.8204166941528396E-4</v>
+        <v>5.5732365802783701E-3</v>
       </c>
       <c r="G100">
-        <v>7.1698376637975103E-4</v>
+        <v>4.0689924661150003E-3</v>
       </c>
       <c r="H100">
-        <v>7.2361989397557304E-4</v>
+        <v>4.1066535045521501E-3</v>
+      </c>
+      <c r="I100">
+        <v>18.271869219999999</v>
       </c>
     </row>
-    <row r="101" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="101" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E101" s="1">
         <v>44776.698611111111</v>
       </c>
       <c r="F101">
-        <v>6.8230783756815302E-4</v>
+        <v>5.13099269333694E-3</v>
       </c>
       <c r="G101">
-        <v>5.1341501153308496E-4</v>
+        <v>3.8609092961429401E-3</v>
       </c>
       <c r="H101">
-        <v>5.0671515553957702E-4</v>
+        <v>3.81052600834838E-3</v>
+      </c>
+      <c r="I101">
+        <v>17.106053899999999</v>
       </c>
     </row>
-    <row r="102" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="102" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E102" s="1">
         <v>44776.709027777775</v>
       </c>
       <c r="F102">
-        <v>4.8825608108944398E-4</v>
+        <v>5.3212337093761601E-3</v>
       </c>
       <c r="G102">
-        <v>3.6351370550483997E-4</v>
+        <v>3.9617353648852298E-3</v>
       </c>
       <c r="H102">
-        <v>3.6292172178298298E-4</v>
+        <v>3.9552836608285503E-3</v>
+      </c>
+      <c r="I102">
+        <v>15.6821315249999</v>
       </c>
     </row>
-    <row r="103" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="103" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E103" s="1">
         <v>44776.719444444447</v>
       </c>
       <c r="F103">
-        <v>4.0077653523385402E-4</v>
+        <v>5.0246263053807796E-3</v>
       </c>
       <c r="G103">
-        <v>3.0147754661757399E-4</v>
+        <v>3.7796923673478599E-3</v>
       </c>
       <c r="H103">
-        <v>2.98156228743596E-4</v>
+        <v>3.7380522520664501E-3</v>
+      </c>
+      <c r="I103">
+        <v>15.17592808</v>
       </c>
     </row>
-    <row r="104" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="104" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E104" s="1">
         <v>44776.729861111111</v>
       </c>
       <c r="F104">
-        <v>2.8406229446980902E-4</v>
+        <v>4.6094203043980297E-3</v>
       </c>
       <c r="G104">
-        <v>2.1045785151038799E-4</v>
+        <v>3.4150561791017799E-3</v>
       </c>
       <c r="H104">
-        <v>2.0862225839116699E-4</v>
+        <v>3.38527038793886E-3</v>
+      </c>
+      <c r="I104">
+        <v>14.28611474</v>
       </c>
     </row>
-    <row r="105" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="105" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E105" s="1">
         <v>44776.740277777775</v>
       </c>
       <c r="F105">
-        <v>1.15579019054127E-4</v>
-      </c>
-      <c r="G105" s="2">
-        <v>8.5382289286336493E-5</v>
-      </c>
-      <c r="H105" s="2">
-        <v>8.5098354639134103E-5</v>
+        <v>3.2871035946504899E-3</v>
+      </c>
+      <c r="G105">
+        <v>2.4282991180632702E-3</v>
+      </c>
+      <c r="H105">
+        <v>2.4202239275499301E-3</v>
+      </c>
+      <c r="I105">
+        <v>11.657254006500001</v>
       </c>
     </row>
-    <row r="106" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="106" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E106" s="1">
         <v>44776.750694444447</v>
       </c>
-      <c r="F106" s="2">
-        <v>4.8066690553333703E-5</v>
-      </c>
-      <c r="G106" s="2">
-        <v>3.5339869466431098E-5</v>
-      </c>
-      <c r="H106" s="2">
-        <v>3.4809136627914099E-5</v>
+      <c r="F106">
+        <v>1.53994824810323E-3</v>
+      </c>
+      <c r="G106">
+        <v>1.13220963305243E-3</v>
+      </c>
+      <c r="H106">
+        <v>1.11520615110727E-3</v>
+      </c>
+      <c r="I106">
+        <v>9.6026396404999996</v>
       </c>
     </row>
-    <row r="107" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="107" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E107" s="1">
         <v>44776.761111111111</v>
       </c>
-      <c r="F107" s="2">
-        <v>3.9194224418457197E-5</v>
-      </c>
-      <c r="G107" s="2">
-        <v>2.7627215109462799E-5</v>
-      </c>
-      <c r="H107" s="2">
-        <v>2.7082074992085E-5</v>
+      <c r="F107">
+        <v>1.2889775231266999E-3</v>
+      </c>
+      <c r="G107">
+        <v>9.0857415429634804E-4</v>
+      </c>
+      <c r="H107">
+        <v>8.9064617208336203E-4</v>
+      </c>
+      <c r="I107">
+        <v>9.2022879035000003</v>
       </c>
     </row>
-    <row r="108" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="108" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E108" s="1">
         <v>44776.771527777775</v>
       </c>
-      <c r="F108" s="2">
-        <v>2.2204912325750299E-5</v>
-      </c>
-      <c r="G108" s="2">
-        <v>1.37545459257828E-5</v>
-      </c>
-      <c r="H108" s="2">
-        <v>1.30656730647897E-5</v>
+      <c r="F108">
+        <v>8.0868477222856099E-4</v>
+      </c>
+      <c r="G108">
+        <v>5.0092932934170495E-4</v>
+      </c>
+      <c r="H108">
+        <v>4.7584114233522798E-4</v>
+      </c>
+      <c r="I108">
+        <v>7.7941709709999998</v>
       </c>
     </row>
-    <row r="109" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="109" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E109" s="1">
         <v>44776.781944444447</v>
       </c>
-      <c r="F109" s="2">
-        <v>5.7209591914661297E-6</v>
-      </c>
-      <c r="G109" s="2">
-        <v>3.9840848125274297E-6</v>
-      </c>
-      <c r="H109" s="2">
-        <v>3.8862209671067402E-6</v>
+      <c r="F109">
+        <v>2.5053512897688302E-4</v>
+      </c>
+      <c r="G109">
+        <v>1.7447305057741801E-4</v>
+      </c>
+      <c r="H109">
+        <v>1.7018734772214199E-4</v>
+      </c>
+      <c r="I109">
+        <v>5.7733400259999996</v>
       </c>
     </row>
-    <row r="110" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="110" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E110" s="1">
         <v>44776.792361111111</v>
       </c>
-      <c r="F110" s="2">
-        <v>4.6235635463227896E-6</v>
-      </c>
-      <c r="G110" s="2">
-        <v>2.6842380066374601E-6</v>
-      </c>
-      <c r="H110" s="2">
-        <v>2.6515503817109999E-6</v>
+      <c r="F110">
+        <v>2.17042463423721E-4</v>
+      </c>
+      <c r="G110">
+        <v>1.2600532544730899E-4</v>
+      </c>
+      <c r="H110">
+        <v>1.24470880737367E-4</v>
+      </c>
+      <c r="I110">
+        <v>5.1560535449999998</v>
       </c>
     </row>
-    <row r="111" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="111" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E111" s="1">
         <v>44776.802777777775</v>
       </c>
-      <c r="F111" s="2">
-        <v>2.0442095213971602E-6</v>
+      <c r="F111">
+        <v>1.0496417991406E-4</v>
       </c>
       <c r="G111" s="2">
-        <v>1.4058412218177401E-6</v>
+        <v>7.2185834863316203E-5</v>
       </c>
       <c r="H111" s="2">
-        <v>1.3810199356689E-6</v>
+        <v>7.0911334416404696E-5</v>
+      </c>
+      <c r="I111">
+        <v>4.4556949205</v>
       </c>
     </row>
-    <row r="112" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="112" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E112" s="1">
         <v>44776.813194444447</v>
       </c>
       <c r="F112" s="2">
-        <v>8.4608754407049798E-7</v>
+        <v>4.98276871901227E-5</v>
       </c>
       <c r="G112" s="2">
-        <v>5.6447780454141204E-7</v>
+        <v>3.3243159845828698E-5</v>
       </c>
       <c r="H112" s="2">
-        <v>5.5071188114452805E-7</v>
+        <v>3.24324587199272E-5</v>
+      </c>
+      <c r="I112">
+        <v>3.5644504299999999</v>
       </c>
     </row>
-    <row r="113" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="113" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E113" s="1">
         <v>44776.823611111111</v>
       </c>
       <c r="F113" s="2">
-        <v>7.9548858694861903E-7</v>
+        <v>4.7846362469734101E-5</v>
       </c>
       <c r="G113" s="2">
-        <v>5.4522666378771696E-7</v>
+        <v>3.2793823835698597E-5</v>
       </c>
       <c r="H113" s="2">
-        <v>5.2540175849865201E-7</v>
+        <v>3.1601412504950497E-5</v>
+      </c>
+      <c r="I113">
+        <v>3.44414985149999</v>
       </c>
     </row>
-    <row r="114" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="114" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E114" s="1">
         <v>44776.834027777775</v>
       </c>
       <c r="F114" s="2">
-        <v>9.2995385842568605E-7</v>
+        <v>5.58148706582288E-5</v>
       </c>
       <c r="G114" s="2">
-        <v>6.09978026661199E-7</v>
+        <v>3.6610251523688897E-5</v>
       </c>
       <c r="H114" s="2">
-        <v>6.0747217409804298E-7</v>
+        <v>3.64598528387605E-5</v>
+      </c>
+      <c r="I114">
+        <v>3.4561308749999999</v>
       </c>
     </row>
-    <row r="115" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="115" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E115" s="1">
         <v>44776.844444444447</v>
       </c>
       <c r="F115" s="2">
-        <v>7.1353611262290904E-7</v>
+        <v>4.5000964263210298E-5</v>
       </c>
       <c r="G115" s="2">
-        <v>4.60290903372103E-7</v>
+        <v>2.9029412986223601E-5</v>
       </c>
       <c r="H115" s="2">
-        <v>4.4720960232561898E-7</v>
+        <v>2.8204407565554602E-5</v>
+      </c>
+      <c r="I115">
+        <v>3.188326338</v>
       </c>
     </row>
-    <row r="116" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="116" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E116" s="1">
         <v>44776.854861111111</v>
       </c>
       <c r="F116" s="2">
-        <v>4.4749196250294002E-7</v>
+        <v>3.0130741794009601E-5</v>
       </c>
       <c r="G116" s="2">
-        <v>3.0123017056390899E-7</v>
+        <v>2.0282573208857299E-5</v>
       </c>
       <c r="H116" s="2">
-        <v>3.0172746386311302E-7</v>
+        <v>2.0316057198426402E-5</v>
+      </c>
+      <c r="I116">
+        <v>2.8661624744999998</v>
       </c>
     </row>
-    <row r="117" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="117" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E117" s="1">
         <v>44776.865277777775</v>
       </c>
       <c r="F117" s="2">
-        <v>2.97598488557786E-7</v>
+        <v>2.1020868956811798E-5</v>
       </c>
       <c r="G117" s="2">
-        <v>2.3196495809394001E-7</v>
+        <v>1.6384844595069299E-5</v>
       </c>
       <c r="H117" s="2">
-        <v>2.35107426414113E-7</v>
+        <v>1.6606812841669698E-5</v>
+      </c>
+      <c r="I117">
+        <v>2.6512377974999999</v>
       </c>
     </row>
-    <row r="118" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="118" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E118" s="1">
         <v>44776.875694444447</v>
       </c>
       <c r="F118" s="2">
-        <v>2.91656407736742E-7</v>
+        <v>2.0632970383662501E-5</v>
       </c>
       <c r="G118" s="2">
-        <v>2.23014422514708E-7</v>
+        <v>1.57769548440178E-5</v>
       </c>
       <c r="H118" s="2">
-        <v>2.2202552892917499E-7</v>
+        <v>1.5706996456229699E-5</v>
+      </c>
+      <c r="I118">
+        <v>2.6445850609999999</v>
       </c>
     </row>
-    <row r="119" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="119" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E119" s="1">
         <v>44776.917361111111</v>
       </c>
       <c r="F119" s="2">
-        <v>2.38278498467708E-7</v>
+        <v>1.7944875951429599E-5</v>
       </c>
       <c r="G119" s="2">
-        <v>1.72637766353315E-7</v>
+        <v>1.30014387435252E-5</v>
       </c>
       <c r="H119" s="2">
-        <v>1.6952885446824599E-7</v>
+        <v>1.2767304994691E-5</v>
+      </c>
+      <c r="I119">
+        <v>2.3885584199999998</v>
       </c>
     </row>
-    <row r="120" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="120" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E120" s="1">
         <v>44776.948611111111</v>
       </c>
       <c r="F120" s="2">
-        <v>2.7142588960351998E-7</v>
+        <v>1.99608362478804E-5</v>
       </c>
       <c r="G120" s="2">
-        <v>1.9534509780769699E-7</v>
+        <v>1.43658053952108E-5</v>
       </c>
       <c r="H120" s="2">
-        <v>1.8897250739057999E-7</v>
+        <v>1.38971609558558E-5</v>
+      </c>
+      <c r="I120">
+        <v>2.4828400044999999</v>
       </c>
     </row>
-    <row r="121" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="121" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E121" s="1">
         <v>44776.959027777775</v>
       </c>
       <c r="F121" s="2">
-        <v>2.8845317308508E-7</v>
+        <v>2.1097365103920101E-5</v>
       </c>
       <c r="G121" s="2">
-        <v>2.1541480276719E-7</v>
+        <v>1.5755364013596901E-5</v>
       </c>
       <c r="H121" s="2">
-        <v>2.1399739126332401E-7</v>
+        <v>1.5651695027523801E-5</v>
+      </c>
+      <c r="I121">
+        <v>2.5050373965000001</v>
       </c>
     </row>
-    <row r="122" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="122" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E122" s="1">
         <v>44776.969444444447</v>
       </c>
       <c r="F122" s="2">
-        <v>1.7803150855957199E-7</v>
+        <v>1.39144874919424E-5</v>
       </c>
       <c r="G122" s="2">
-        <v>1.33715456593602E-7</v>
+        <v>1.04508581839459E-5</v>
       </c>
       <c r="H122" s="2">
-        <v>1.3279940333071499E-7</v>
+        <v>1.03792618030323E-5</v>
+      </c>
+      <c r="I122">
+        <v>2.248553292</v>
       </c>
     </row>
-    <row r="123" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="123" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E123" s="1">
         <v>44776.979861111111</v>
       </c>
       <c r="F123" s="2">
-        <v>1.3568315097894001E-7</v>
+        <v>1.08806963286294E-5</v>
       </c>
       <c r="G123" s="2">
-        <v>1.0094948792846299E-7</v>
+        <v>8.0953361912696808E-6</v>
       </c>
       <c r="H123" s="2">
-        <v>1.00292044219874E-7</v>
+        <v>8.0426144988607792E-6</v>
+      </c>
+      <c r="I123">
+        <v>2.1564305309999998</v>
       </c>
     </row>
-    <row r="124" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="124" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E124" s="1">
         <v>44776.990277777775</v>
       </c>
       <c r="F124" s="2">
-        <v>1.86896842999386E-7</v>
+        <v>1.4707523941653399E-5</v>
       </c>
       <c r="G124" s="2">
-        <v>1.2465689326174701E-7</v>
+        <v>9.8096587014311299E-6</v>
       </c>
       <c r="H124" s="2">
-        <v>1.2059315237547099E-7</v>
+        <v>9.4898696381410604E-6</v>
+      </c>
+      <c r="I124">
+        <v>2.2236830264999998</v>
       </c>
     </row>
-    <row r="125" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="125" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E125" s="1">
         <v>44777.000694444447</v>
       </c>
       <c r="F125" s="2">
-        <v>1.5120622219659301E-7</v>
+        <v>1.19575360197737E-5</v>
       </c>
       <c r="G125" s="2">
-        <v>1.1480211508073799E-7</v>
+        <v>9.0786636044787495E-6</v>
       </c>
       <c r="H125" s="2">
-        <v>1.13534428409363E-7</v>
+        <v>8.97841370194367E-6</v>
+      </c>
+      <c r="I125">
+        <v>2.2059633774999998</v>
       </c>
     </row>
-    <row r="126" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="126" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E126" s="1"/>
     </row>
-    <row r="127" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="127" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E127" s="1"/>
     </row>
-    <row r="128" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="128" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E128" s="1"/>
     </row>
     <row r="129" spans="5:5" x14ac:dyDescent="0.25">
